--- a/assets/cs1/sheet/pydasa_cs1_dim_vars.xlsx
+++ b/assets/cs1/sheet/pydasa_cs1_dim_vars.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bd4428830306c10d/Documents/GitHub/DASA-Design/PyDASA-Case-Studies/assets/cs1/sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1863" documentId="8_{77ABEE66-5EB5-4456-89E8-5A5C11573875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17A19308-5D82-4186-A608-B57F4B80BF14}"/>
+  <xr:revisionPtr revIDLastSave="1915" documentId="8_{77ABEE66-5EB5-4456-89E8-5A5C11573875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088299E4-1262-4CAF-8BCB-B3A46B1A4144}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{EABAE1E3-9871-4CDD-80AF-2EA34DC987B5}"/>
+    <workbookView xWindow="-80" yWindow="0" windowWidth="12960" windowHeight="15360" activeTab="1" xr2:uid="{EABAE1E3-9871-4CDD-80AF-2EA34DC987B5}"/>
   </bookViews>
   <sheets>
     <sheet name="dflt_relevance_lt@3FDUs" sheetId="1" r:id="rId1"/>
     <sheet name="opti_relevance_lt@3FDUs " sheetId="25" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="22" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="10" r:id="rId4"/>
-    <sheet name="opti_relevance_lt@3FDUs  (2)" sheetId="26" r:id="rId5"/>
+    <sheet name="opti_relevance_lt@3FDUs  (2)" sheetId="26" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="45">
   <si>
     <t>name</t>
   </si>
@@ -153,21 +152,6 @@
     <t>adjusted_rate</t>
   </si>
   <si>
-    <t>Bienvenida</t>
-  </si>
-  <si>
-    <t>Entrenamiento</t>
-  </si>
-  <si>
-    <t>Mentorías</t>
-  </si>
-  <si>
-    <t>ACTIVIDAD</t>
-  </si>
-  <si>
-    <t>TIEMPO [h]</t>
-  </si>
-  <si>
     <t>I*T^-1</t>
   </si>
   <si>
@@ -180,133 +164,13 @@
     <t>CUSTOM</t>
   </si>
   <si>
-    <t>CONCAT("{'low': ", [@[_std_min]], ", 'high': ",[@[_std_max]],"}")</t>
+    <t>E*T^-1</t>
   </si>
   <si>
-    <t>CONCAT("{'scale': ",[@[_std_max]],"}")</t>
+    <t>E</t>
   </si>
   <si>
-    <t>brallanlaverde@gmail.com</t>
-  </si>
-  <si>
-    <t>pablojuniorsierra@gmail.com</t>
-  </si>
-  <si>
-    <t>gabriela_guadalupe03@hotmail.com</t>
-  </si>
-  <si>
-    <t>dfshsdfkyhwerh@gmail.com</t>
-  </si>
-  <si>
-    <t>harsanenciso@gmail.com</t>
-  </si>
-  <si>
-    <t>juancazzhr@gmail.com</t>
-  </si>
-  <si>
-    <t>oscardavid.rp34@gmail.com</t>
-  </si>
-  <si>
-    <t>n.villegasc09@gmail.com</t>
-  </si>
-  <si>
-    <t>rafa.bravv@gmail.com</t>
-  </si>
-  <si>
-    <t>santiago.morales@utec.edu.pe</t>
-  </si>
-  <si>
-    <t>luisfelipechilis24@gmail.com</t>
-  </si>
-  <si>
-    <t>carloseduardo7366@gmail.com</t>
-  </si>
-  <si>
-    <t>dasamu88@gmail.com</t>
-  </si>
-  <si>
-    <t>fernando8monzon@gmail.com</t>
-  </si>
-  <si>
-    <t>ing.ajaramilloc@gmail.com</t>
-  </si>
-  <si>
-    <t>rorygrimmmusic@gmail.com</t>
-  </si>
-  <si>
-    <t>onatejose1307@gmail.com</t>
-  </si>
-  <si>
-    <t>sdsch24@gmail.com</t>
-  </si>
-  <si>
-    <t>mbaku478@gmail.com</t>
-  </si>
-  <si>
-    <t>millerandresoc@gmail.com</t>
-  </si>
-  <si>
-    <t>davida.pachonl@gmail.com</t>
-  </si>
-  <si>
-    <t>valentina0519@gmail.com</t>
-  </si>
-  <si>
-    <t>cvences@exatec.tec.mx</t>
-  </si>
-  <si>
-    <t>2cristianruiz5@gmail.com</t>
-  </si>
-  <si>
-    <t>gabtov2002@gmail.com</t>
-  </si>
-  <si>
-    <t>alonsoalejo11@gmail.com</t>
-  </si>
-  <si>
-    <t>mazouribeestefania@gmail.com</t>
-  </si>
-  <si>
-    <t>juanfelipehernandezpaez@gmail.com</t>
-  </si>
-  <si>
-    <t>danielatorr1722@gmail.com</t>
-  </si>
-  <si>
-    <t>arsebmar@outlook.com</t>
-  </si>
-  <si>
-    <t>saintria14@gmail.com</t>
-  </si>
-  <si>
-    <t>sa.hernandezd1@uniandes.edu.co</t>
-  </si>
-  <si>
-    <t>luisarojas25.31@gmail.com</t>
-  </si>
-  <si>
-    <t>danieljreyes003@gmail.com</t>
-  </si>
-  <si>
-    <t>galoget.latorre@gmail.com</t>
-  </si>
-  <si>
-    <t>duqueruizjeronimo@gmail.com</t>
-  </si>
-  <si>
-    <t>amesticapatricio@gmail.com</t>
-  </si>
-  <si>
-    <t>felipem2001@gmail.com</t>
-  </si>
-  <si>
-    <t>sergioalejandro.casta@gmail.com</t>
-  </si>
-  <si>
-    <t>Mentorias</t>
-  </si>
-  <si>
-    <t>Trabajo Individual</t>
+    <t>D*E^-1</t>
   </si>
 </sst>
 </file>
@@ -317,7 +181,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,14 +322,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,12 +503,6 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFE2F3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -812,7 +664,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -841,16 +693,12 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -896,7 +744,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="69">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -970,9 +818,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1157,384 +1002,6 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TIEMPO [h]</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="accent1"/>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="accent2"/>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="accent3"/>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="35000"/>
-                      <a:lumOff val="65000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:round/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$D$4:$D$6</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Bienvenida</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Entrenamiento</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Mentorías</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$4:$E$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6C4E-4813-A8D4-2E3B92F9A87F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
-        </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$29</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TIEMPO [h]</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -1631,36 +1098,55 @@
               </c:ext>
             </c:extLst>
           </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$D$30:$D$31</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Mentorias</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Trabajo Individual</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$30:$E$31</c:f>
+              <c:f>Sheet1!#REF!</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.83333333333333337</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredSeriesTitle>
+                <c15:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>#REF!</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c15:tx>
+              </c15:filteredSeriesTitle>
+            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:filteredCategoryTitle>
+                <c15:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                  </c:multiLvlStrRef>
+                </c15:cat>
+              </c15:filteredCategoryTitle>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-F19C-4A67-867D-F08EE1DB8DFC}"/>
             </c:ext>
@@ -1776,567 +1262,7 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="259">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:styleClr val="auto"/>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:styleClr val="auto"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" b="1" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="63500" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="20000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:effectLst>
-        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="10000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-      <a:scene3d>
-        <a:camera prst="orthographicFront"/>
-        <a:lightRig rig="threePt" dir="t"/>
-      </a:scene3d>
-      <a:sp3d>
-        <a:bevelT w="127000" h="127000"/>
-        <a:bevelB w="127000" h="127000"/>
-      </a:sp3d>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDash"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2859,52 +1785,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>641350</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>127528</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>35983</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>156103</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B126E40F-B180-7EBA-65FD-17214872E05E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>514349</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>25399</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2923,7 +1813,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2933,42 +1823,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00779A18-6B29-4DFE-86A0-3F8F27AE11B5}" name="Table1" displayName="Table1" ref="A1:U144" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00779A18-6B29-4DFE-86A0-3F8F27AE11B5}" name="Table1" displayName="Table1" ref="A1:U144" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="A1:U144" xr:uid="{00779A18-6B29-4DFE-86A0-3F8F27AE11B5}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{D4736AB9-B625-46BB-8450-90A78651DB74}" name="_idx" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{57B02955-84ED-43C2-9050-83315840EE61}" name="dm" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{94800A5C-6B37-4055-946D-D0D09875D730}" name="_sym" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{AA22D112-29A2-4A6D-A9EA-C97DCE3D6213}" name="_alias" dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{D4736AB9-B625-46BB-8450-90A78651DB74}" name="_idx" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{57B02955-84ED-43C2-9050-83315840EE61}" name="dm" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{94800A5C-6B37-4055-946D-D0D09875D730}" name="_sym" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{AA22D112-29A2-4A6D-A9EA-C97DCE3D6213}" name="_alias" dataDxfId="63">
       <calculatedColumnFormula>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{38B1CC33-FB88-4CE3-BF7C-5835696B216A}" name="_fwk" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{BB870EB7-B325-473A-85A9-78BEEABC2AB4}" name="name" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{8A0C40DF-C757-43E6-9C5D-AD93E056E738}" name="description" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{6C54E7CB-2744-4933-AE1F-20B2E9B3C4CB}" name="relevant" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{A1FAE8DA-AD48-476D-AD7F-9B22A387B8CD}" name="_cat" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{75955A00-9C24-4F7C-9544-0BB53EB49E6F}" name="_dims" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{21B8938E-F128-4D82-8449-6839F35D8576}" name="_units" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{B2D21467-EAEF-466D-AC27-74D823FCD775}" name="_min" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{45F223B2-B242-43AC-BE09-0CBE9E2CC3B2}" name="_max" dataDxfId="55"/>
-    <tableColumn id="14" xr3:uid="{C13AD127-3F9A-44BC-A2F3-D4671045828D}" name="_mean" dataDxfId="54"/>
-    <tableColumn id="15" xr3:uid="{8C04B261-792E-4EB6-A253-74DE1709C591}" name="_std_units" dataDxfId="53">
+    <tableColumn id="5" xr3:uid="{38B1CC33-FB88-4CE3-BF7C-5835696B216A}" name="_fwk" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{BB870EB7-B325-473A-85A9-78BEEABC2AB4}" name="name" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{8A0C40DF-C757-43E6-9C5D-AD93E056E738}" name="description" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{6C54E7CB-2744-4933-AE1F-20B2E9B3C4CB}" name="relevant" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{A1FAE8DA-AD48-476D-AD7F-9B22A387B8CD}" name="_cat" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{75955A00-9C24-4F7C-9544-0BB53EB49E6F}" name="_dims" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{21B8938E-F128-4D82-8449-6839F35D8576}" name="_units" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{B2D21467-EAEF-466D-AC27-74D823FCD775}" name="_min" dataDxfId="55"/>
+    <tableColumn id="13" xr3:uid="{45F223B2-B242-43AC-BE09-0CBE9E2CC3B2}" name="_max" dataDxfId="54"/>
+    <tableColumn id="14" xr3:uid="{C13AD127-3F9A-44BC-A2F3-D4671045828D}" name="_mean" dataDxfId="53"/>
+    <tableColumn id="15" xr3:uid="{8C04B261-792E-4EB6-A253-74DE1709C591}" name="_std_units" dataDxfId="52">
       <calculatedColumnFormula>Table1[[#This Row],[_units]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{15E76D01-467D-4868-B8DC-E75022C2CA75}" name="_std_min" dataDxfId="52">
+    <tableColumn id="16" xr3:uid="{15E76D01-467D-4868-B8DC-E75022C2CA75}" name="_std_min" dataDxfId="51">
       <calculatedColumnFormula>Table1[[#This Row],[_min]]*1024000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{6811C172-5351-48A6-9EEF-3DB47ECAA99B}" name="_std_max" dataDxfId="51">
+    <tableColumn id="17" xr3:uid="{6811C172-5351-48A6-9EEF-3DB47ECAA99B}" name="_std_max" dataDxfId="50">
       <calculatedColumnFormula>Table1[[#This Row],[_max]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{DFBF67C9-AE09-412C-BEA7-1949852BC694}" name="_std_mean" dataDxfId="50">
+    <tableColumn id="18" xr3:uid="{DFBF67C9-AE09-412C-BEA7-1949852BC694}" name="_std_mean" dataDxfId="49">
       <calculatedColumnFormula>Table1[[#This Row],[_mean]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{733D523E-5881-4E29-BCF9-4A5022F874AB}" name="_dist_type" dataDxfId="49"/>
-    <tableColumn id="21" xr3:uid="{04715694-390E-4375-AA9A-7BED2789FE82}" name="_depends" dataDxfId="48">
+    <tableColumn id="19" xr3:uid="{733D523E-5881-4E29-BCF9-4A5022F874AB}" name="_dist_type" dataDxfId="48"/>
+    <tableColumn id="21" xr3:uid="{04715694-390E-4375-AA9A-7BED2789FE82}" name="_depends" dataDxfId="47">
       <calculatedColumnFormula>_xlfn.CONCAT("[","]")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{778C4332-7292-4634-BBE1-54886DA144B7}" name="_dist_params" dataDxfId="47">
+    <tableColumn id="20" xr3:uid="{778C4332-7292-4634-BBE1-54886DA144B7}" name="_dist_params" dataDxfId="46">
       <calculatedColumnFormula>_xlfn.CONCAT("{'scale': 1/",Table1[[#This Row],[_std_mean]],"}")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2977,42 +1867,42 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3D21A2E2-6FDE-41B1-A172-0C806AF125C1}" name="Table16" displayName="Table16" ref="A1:U144" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3D21A2E2-6FDE-41B1-A172-0C806AF125C1}" name="Table16" displayName="Table16" ref="A1:U144" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
   <autoFilter ref="A1:U144" xr:uid="{00779A18-6B29-4DFE-86A0-3F8F27AE11B5}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{E96E2AA0-8DB2-46CE-BB8F-4189E1217666}" name="_idx" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{19562959-93B9-4DFC-90B7-BAF46A5EB629}" name="dm" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{C0922357-8F1C-46E9-8BEE-DF8DFC3F101A}" name="_sym" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{F5916D6C-6194-4133-9DA2-A61A2E998E11}" name="_alias" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{E96E2AA0-8DB2-46CE-BB8F-4189E1217666}" name="_idx" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{19562959-93B9-4DFC-90B7-BAF46A5EB629}" name="dm" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{C0922357-8F1C-46E9-8BEE-DF8DFC3F101A}" name="_sym" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{F5916D6C-6194-4133-9DA2-A61A2E998E11}" name="_alias" dataDxfId="40">
       <calculatedColumnFormula>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{D9F4B58F-2FEB-43CB-8591-B3F8C1DD8F82}" name="_fwk" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{5DC04DB2-218E-4530-B504-5E6F93501C77}" name="name" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{07C9BC1E-0BC6-4A0E-9BC0-5FD0222B6A67}" name="description" dataDxfId="38"/>
-    <tableColumn id="8" xr3:uid="{BD111ACD-C35B-4325-AD81-804789CFFF43}" name="relevant" dataDxfId="37"/>
-    <tableColumn id="9" xr3:uid="{F962872D-781B-43A6-A909-EAAF584AAFED}" name="_cat" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{1D4A6078-87FF-4839-9259-3D9CC1B125AC}" name="_dims" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{480D0F01-5227-4728-9049-99D90163FFCC}" name="_units" dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{519F85F3-E215-4884-BA67-BA68A24166FE}" name="_min" dataDxfId="33"/>
-    <tableColumn id="13" xr3:uid="{9DFBB1C3-AE4A-46A4-B6FB-2711F43A4782}" name="_max" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{DD09887F-BAAF-42FE-A36D-E4E3A7AD2E97}" name="_mean" dataDxfId="31"/>
-    <tableColumn id="15" xr3:uid="{F4D0FF79-0965-4C61-AF45-C8DA836E5D14}" name="_std_units" dataDxfId="30">
+    <tableColumn id="5" xr3:uid="{D9F4B58F-2FEB-43CB-8591-B3F8C1DD8F82}" name="_fwk" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{5DC04DB2-218E-4530-B504-5E6F93501C77}" name="name" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{07C9BC1E-0BC6-4A0E-9BC0-5FD0222B6A67}" name="description" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{BD111ACD-C35B-4325-AD81-804789CFFF43}" name="relevant" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{F962872D-781B-43A6-A909-EAAF584AAFED}" name="_cat" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{1D4A6078-87FF-4839-9259-3D9CC1B125AC}" name="_dims" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{480D0F01-5227-4728-9049-99D90163FFCC}" name="_units" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{519F85F3-E215-4884-BA67-BA68A24166FE}" name="_min" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{9DFBB1C3-AE4A-46A4-B6FB-2711F43A4782}" name="_max" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{DD09887F-BAAF-42FE-A36D-E4E3A7AD2E97}" name="_mean" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{F4D0FF79-0965-4C61-AF45-C8DA836E5D14}" name="_std_units" dataDxfId="29">
       <calculatedColumnFormula>Table16[[#This Row],[_units]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{22E67E8B-60AE-42B4-A1A9-1C4A3C432FBC}" name="_std_min" dataDxfId="29">
+    <tableColumn id="16" xr3:uid="{22E67E8B-60AE-42B4-A1A9-1C4A3C432FBC}" name="_std_min" dataDxfId="28">
       <calculatedColumnFormula>Table16[[#This Row],[_min]]*1024000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{89B23AEC-0059-4E54-8878-0E24B566EF2C}" name="_std_max" dataDxfId="28">
+    <tableColumn id="17" xr3:uid="{89B23AEC-0059-4E54-8878-0E24B566EF2C}" name="_std_max" dataDxfId="27">
       <calculatedColumnFormula>Table16[[#This Row],[_max]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{68E66582-B105-4854-8956-872306E20ABE}" name="_std_mean" dataDxfId="27">
+    <tableColumn id="18" xr3:uid="{68E66582-B105-4854-8956-872306E20ABE}" name="_std_mean" dataDxfId="26">
       <calculatedColumnFormula>Table16[[#This Row],[_mean]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{FA38C013-A923-4FB8-8E97-7350A5669857}" name="_dist_type" dataDxfId="26"/>
-    <tableColumn id="21" xr3:uid="{3E46D881-4D2E-4B12-BD2E-71EF89CFAD3B}" name="_depends" dataDxfId="25">
+    <tableColumn id="19" xr3:uid="{FA38C013-A923-4FB8-8E97-7350A5669857}" name="_dist_type" dataDxfId="25"/>
+    <tableColumn id="21" xr3:uid="{3E46D881-4D2E-4B12-BD2E-71EF89CFAD3B}" name="_depends" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.CONCAT("[","]")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{39D59493-0F3B-499F-92C3-25B7D1110CC6}" name="_dist_params" dataDxfId="24">
+    <tableColumn id="20" xr3:uid="{39D59493-0F3B-499F-92C3-25B7D1110CC6}" name="_dist_params" dataDxfId="23">
       <calculatedColumnFormula>_xlfn.CONCAT("{'scale': 1/",Table16[[#This Row],[_std_mean]],"}")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3021,28 +1911,6 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C1FCF3F4-6D16-44BB-B52B-B1C828432D4A}" name="Table3" displayName="Table3" ref="D3:E6" totalsRowShown="0">
-  <autoFilter ref="D3:E6" xr:uid="{C1FCF3F4-6D16-44BB-B52B-B1C828432D4A}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E0258CE0-67C3-4CDC-9DB1-A04C59E56AF1}" name="ACTIVIDAD"/>
-    <tableColumn id="2" xr3:uid="{5849C093-305D-4A07-BC18-8993B8E571BB}" name="TIEMPO [h]"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{26812C76-01D5-4C67-84ED-D08ACF1C4FC2}" name="Table33" displayName="Table33" ref="D29:E31" totalsRowShown="0">
-  <autoFilter ref="D29:E31" xr:uid="{26812C76-01D5-4C67-84ED-D08ACF1C4FC2}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{73418CB3-D5C8-44A9-9449-1C5D725C93BD}" name="ACTIVIDAD"/>
-    <tableColumn id="2" xr3:uid="{9F26E105-7A65-4541-9F3D-F1724FC489BC}" name="TIEMPO [h]" dataDxfId="23"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5306AE0D-0198-45F0-9B51-719BC1DE52A4}" name="Table167" displayName="Table167" ref="A1:U144" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A1:U144" xr:uid="{00779A18-6B29-4DFE-86A0-3F8F27AE11B5}"/>
   <tableColumns count="21">
@@ -3502,15 +2370,15 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{1}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{1}</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
         <v>lambda_tas_1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " arrival rate")</f>
@@ -3527,7 +2395,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>4</v>
@@ -3579,15 +2447,15 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{1}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{1}</v>
       </c>
       <c r="D3" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
         <v>mu_tas_1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " service rate")</f>
@@ -3604,7 +2472,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>4</v>
@@ -3664,7 +2532,7 @@
         <v>err_tas_1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " error probability")</f>
@@ -3681,7 +2549,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>31</v>
@@ -3732,15 +2600,15 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{1}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{1}</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
         <v>chi_tas_1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " departure rate")</f>
@@ -3757,7 +2625,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>4</v>
@@ -3794,7 +2662,7 @@
       </c>
       <c r="T5" s="1" t="str">
         <f>_xlfn.CONCAT("['", C3, "' , '", C4, "']")</f>
-        <v>['\\mu_{1}' , 'err_{1}']</v>
+        <v>['\mu_{1}' , 'err_{1}']</v>
       </c>
       <c r="U5" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -3817,7 +2685,7 @@
         <v>c_tas_1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " resourses")</f>
@@ -3834,7 +2702,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>7</v>
@@ -3894,7 +2762,7 @@
         <v>K_tas_1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " q-capacity")</f>
@@ -3911,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>7</v>
@@ -3963,15 +2831,15 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{1}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{1}</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
         <v>delta_tas_1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " req data density")</f>
@@ -3988,7 +2856,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -4047,7 +2915,7 @@
         <v>L_tas_1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " mean processing requests")</f>
@@ -4064,7 +2932,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>7</v>
@@ -4101,7 +2969,7 @@
       </c>
       <c r="T9" s="1" t="str">
         <f>_xlfn.CONCAT("['", C2, "' , '", C3, "' , '", C6, "' , '", C7, "']")</f>
-        <v>['\\lambda_{1}' , '\\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
+        <v>['\lambda_{1}' , '\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
       </c>
       <c r="U9" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -4124,7 +2992,7 @@
         <v>Lq_tas_1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " mean in memory requests")</f>
@@ -4141,7 +3009,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>7</v>
@@ -4178,7 +3046,7 @@
       </c>
       <c r="T10" s="1" t="str">
         <f>_xlfn.CONCAT("['", C2, "' , '", C3, "' , '", C6, "' , '", C7, "']")</f>
-        <v>['\\lambda_{1}' , '\\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
+        <v>['\lambda_{1}' , '\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
       </c>
       <c r="U10" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -4201,7 +3069,7 @@
         <v>W_tas_1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " mean time to answer")</f>
@@ -4226,10 +3094,10 @@
       <c r="L11" s="1">
         <v>0</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="10">
         <v>1.8018018018018001E-3</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="10">
         <v>1.8018018018018001E-3</v>
       </c>
       <c r="O11" s="1" t="str">
@@ -4253,7 +3121,7 @@
       </c>
       <c r="T11" s="1" t="str">
         <f>_xlfn.CONCAT("['", C5, "' , '", C9, "']")</f>
-        <v>['\\chi_{1}' , 'L_{1}']</v>
+        <v>['\chi_{1}' , 'L_{1}']</v>
       </c>
       <c r="U11" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -4276,7 +3144,7 @@
         <v>Wq_tas_1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table1[[#This Row],[dm]], " mean time in buffer")</f>
@@ -4301,10 +3169,10 @@
       <c r="L12" s="1">
         <v>0</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="10">
         <v>6.9069069069068996E-4</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="10">
         <v>6.9069069069068996E-4</v>
       </c>
       <c r="O12" s="1" t="str">
@@ -4328,7 +3196,7 @@
       </c>
       <c r="T12" s="1" t="str">
         <f>_xlfn.CONCAT("['", C5, "' , '", C10, "']")</f>
-        <v>['\\chi_{1}' , 'Lq_{1}']</v>
+        <v>['\chi_{1}' , 'Lq_{1}']</v>
       </c>
       <c r="U12" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -4344,8 +3212,8 @@
         <v>2</v>
       </c>
       <c r="C13" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{2}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{2}</v>
       </c>
       <c r="D13" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -4373,7 +3241,7 @@
       </c>
       <c r="J13" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K13" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4382,7 +3250,7 @@
       <c r="L13" s="1">
         <v>0.1</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="10">
         <f>2*258.75</f>
         <v>517.5</v>
       </c>
@@ -4428,8 +3296,8 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{2}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{2}</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -4457,7 +3325,7 @@
       </c>
       <c r="J14" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K14" s="1" t="str">
         <f t="shared" si="4"/>
@@ -4541,7 +3409,7 @@
       </c>
       <c r="J15" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K15" s="1" t="str">
         <f t="shared" si="6"/>
@@ -4595,8 +3463,8 @@
         <v>2</v>
       </c>
       <c r="C16" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{2}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{2}</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -4624,7 +3492,7 @@
       </c>
       <c r="J16" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K16" s="1" t="str">
         <f t="shared" si="7"/>
@@ -4663,7 +3531,7 @@
       </c>
       <c r="T16" s="1" t="str">
         <f t="shared" ref="T16" si="8">_xlfn.CONCAT("['", C14, "' , '", C15, "']")</f>
-        <v>['\\mu_{2}' , 'err_{2}']</v>
+        <v>['\mu_{2}' , 'err_{2}']</v>
       </c>
       <c r="U16" s="1" t="str">
         <f t="shared" ref="U16" si="9">_xlfn.CONCAT("{", "}")</f>
@@ -4708,7 +3576,7 @@
       </c>
       <c r="J17" s="1" t="str">
         <f t="shared" si="10"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K17" s="1" t="str">
         <f t="shared" si="10"/>
@@ -4792,7 +3660,7 @@
       </c>
       <c r="J18" s="1" t="str">
         <f t="shared" si="11"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K18" s="1" t="str">
         <f t="shared" si="11"/>
@@ -4847,8 +3715,8 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{2}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{2}</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -4876,7 +3744,7 @@
       </c>
       <c r="J19" s="1" t="str">
         <f t="shared" si="13"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K19" s="1" t="str">
         <f t="shared" si="13"/>
@@ -4959,7 +3827,7 @@
       </c>
       <c r="J20" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="14"/>
@@ -4998,7 +3866,7 @@
       </c>
       <c r="T20" s="1" t="str">
         <f t="shared" ref="T20" si="15">_xlfn.CONCAT("['", C13, "' , '", C14, "' , '", C17, "' , '", C18, "']")</f>
-        <v>['\\lambda_{2}' , '\\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
+        <v>['\lambda_{2}' , '\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
       </c>
       <c r="U20" s="1" t="str">
         <f t="shared" ref="U20:U23" si="16">_xlfn.CONCAT("{", "}")</f>
@@ -5043,7 +3911,7 @@
       </c>
       <c r="J21" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K21" s="1" t="str">
         <f t="shared" si="17"/>
@@ -5082,7 +3950,7 @@
       </c>
       <c r="T21" s="1" t="str">
         <f t="shared" ref="T21" si="18">_xlfn.CONCAT("['", C13, "' , '", C14, "' , '", C17, "' , '", C18, "']")</f>
-        <v>['\\lambda_{2}' , '\\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
+        <v>['\lambda_{2}' , '\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
       </c>
       <c r="U21" s="1" t="str">
         <f t="shared" si="16"/>
@@ -5136,10 +4004,10 @@
       <c r="L22" s="1">
         <v>0</v>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="10">
         <v>2.2662889518413601E-3</v>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="10">
         <v>2.2662889518413601E-3</v>
       </c>
       <c r="O22" s="1" t="str">
@@ -5164,7 +4032,7 @@
       </c>
       <c r="T22" s="1" t="str">
         <f t="shared" ref="T22" si="20">_xlfn.CONCAT("['", C16, "' , '", C20, "']")</f>
-        <v>['\\chi_{2}' , 'L_{2}']</v>
+        <v>['\chi_{2}' , 'L_{2}']</v>
       </c>
       <c r="U22" s="1" t="str">
         <f t="shared" si="16"/>
@@ -5218,10 +4086,10 @@
       <c r="L23" s="1">
         <v>0</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="10">
         <v>8.3771752326993105E-4</v>
       </c>
-      <c r="N23" s="11">
+      <c r="N23" s="10">
         <v>8.3771752326993105E-4</v>
       </c>
       <c r="O23" s="1" t="str">
@@ -5246,7 +4114,7 @@
       </c>
       <c r="T23" s="1" t="str">
         <f t="shared" ref="T23" si="22">_xlfn.CONCAT("['", C16, "' , '", C21, "']")</f>
-        <v>['\\chi_{2}' , 'Lq_{2}']</v>
+        <v>['\chi_{2}' , 'Lq_{2}']</v>
       </c>
       <c r="U23" s="1" t="str">
         <f t="shared" si="16"/>
@@ -5262,8 +4130,8 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{3}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{3}</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -5291,7 +4159,7 @@
       </c>
       <c r="J24" s="1" t="str">
         <f t="shared" si="23"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K24" s="1" t="str">
         <f t="shared" si="23"/>
@@ -5300,11 +4168,11 @@
       <c r="L24" s="1">
         <v>0.1</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M24" s="10">
         <f>2*173.34525</f>
         <v>346.69049999999999</v>
       </c>
-      <c r="N24" s="11">
+      <c r="N24" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>173.39525</v>
       </c>
@@ -5346,8 +4214,8 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{3}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{3}</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -5375,7 +4243,7 @@
       </c>
       <c r="J25" s="1" t="str">
         <f t="shared" si="24"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K25" s="1" t="str">
         <f t="shared" si="24"/>
@@ -5459,7 +4327,7 @@
       </c>
       <c r="J26" s="1" t="str">
         <f t="shared" si="25"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="25"/>
@@ -5512,8 +4380,8 @@
         <v>3</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{3}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{3}</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -5541,7 +4409,7 @@
       </c>
       <c r="J27" s="1" t="str">
         <f t="shared" si="26"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K27" s="1" t="str">
         <f t="shared" si="26"/>
@@ -5580,7 +4448,7 @@
       </c>
       <c r="T27" s="1" t="str">
         <f t="shared" ref="T27" si="27">_xlfn.CONCAT("['", C25, "' , '", C26, "']")</f>
-        <v>['\\mu_{3}' , 'err_{3}']</v>
+        <v>['\mu_{3}' , 'err_{3}']</v>
       </c>
       <c r="U27" s="1" t="str">
         <f t="shared" ref="U27" si="28">_xlfn.CONCAT("{", "}")</f>
@@ -5625,7 +4493,7 @@
       </c>
       <c r="J28" s="1" t="str">
         <f t="shared" si="29"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K28" s="1" t="str">
         <f t="shared" si="29"/>
@@ -5709,7 +4577,7 @@
       </c>
       <c r="J29" s="1" t="str">
         <f t="shared" si="30"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="30"/>
@@ -5764,8 +4632,8 @@
         <v>3</v>
       </c>
       <c r="C30" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{3}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{3}</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -5793,7 +4661,7 @@
       </c>
       <c r="J30" s="1" t="str">
         <f t="shared" si="32"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="32"/>
@@ -5876,7 +4744,7 @@
       </c>
       <c r="J31" s="1" t="str">
         <f t="shared" si="33"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K31" s="1" t="str">
         <f t="shared" si="33"/>
@@ -5915,7 +4783,7 @@
       </c>
       <c r="T31" s="1" t="str">
         <f t="shared" ref="T31" si="34">_xlfn.CONCAT("['", C24, "' , '", C25, "' , '", C28, "' , '", C29, "']")</f>
-        <v>['\\lambda_{3}' , '\\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
+        <v>['\lambda_{3}' , '\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
       </c>
       <c r="U31" s="1" t="str">
         <f t="shared" ref="U31:U34" si="35">_xlfn.CONCAT("{", "}")</f>
@@ -5960,7 +4828,7 @@
       </c>
       <c r="J32" s="1" t="str">
         <f t="shared" si="36"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K32" s="1" t="str">
         <f t="shared" si="36"/>
@@ -5999,7 +4867,7 @@
       </c>
       <c r="T32" s="1" t="str">
         <f t="shared" ref="T32" si="37">_xlfn.CONCAT("['", C24, "' , '", C25, "' , '", C28, "' , '", C29, "']")</f>
-        <v>['\\lambda_{3}' , '\\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
+        <v>['\lambda_{3}' , '\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
       </c>
       <c r="U32" s="1" t="str">
         <f t="shared" si="35"/>
@@ -6053,10 +4921,10 @@
       <c r="L33" s="1">
         <v>0</v>
       </c>
-      <c r="M33" s="11">
+      <c r="M33" s="10">
         <v>1.89877714005237E-3</v>
       </c>
-      <c r="N33" s="11">
+      <c r="N33" s="10">
         <v>1.89877714005237E-3</v>
       </c>
       <c r="O33" s="1" t="str">
@@ -6081,7 +4949,7 @@
       </c>
       <c r="T33" s="1" t="str">
         <f t="shared" ref="T33" si="39">_xlfn.CONCAT("['", C27, "' , '", C31, "']")</f>
-        <v>['\\chi_{3}' , 'L_{3}']</v>
+        <v>['\chi_{3}' , 'L_{3}']</v>
       </c>
       <c r="U33" s="1" t="str">
         <f t="shared" si="35"/>
@@ -6135,10 +5003,10 @@
       <c r="L34" s="1">
         <v>0</v>
       </c>
-      <c r="M34" s="11">
+      <c r="M34" s="10">
         <v>4.7020571148094899E-4</v>
       </c>
-      <c r="N34" s="11">
+      <c r="N34" s="10">
         <v>4.7020571148094899E-4</v>
       </c>
       <c r="O34" s="1" t="str">
@@ -6163,7 +5031,7 @@
       </c>
       <c r="T34" s="1" t="str">
         <f t="shared" ref="T34" si="41">_xlfn.CONCAT("['", C27, "' , '", C32, "']")</f>
-        <v>['\\chi_{3}' , 'Lq_{3}']</v>
+        <v>['\chi_{3}' , 'Lq_{3}']</v>
       </c>
       <c r="U34" s="1" t="str">
         <f t="shared" si="35"/>
@@ -6179,8 +5047,8 @@
         <v>4</v>
       </c>
       <c r="C35" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{4}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{4}</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -6208,7 +5076,7 @@
       </c>
       <c r="J35" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K35" s="1" t="str">
         <f t="shared" si="42"/>
@@ -6217,11 +5085,11 @@
       <c r="L35" s="1">
         <v>0.1</v>
       </c>
-      <c r="M35" s="11">
+      <c r="M35" s="10">
         <f>2*97.03125</f>
         <v>194.0625</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>97.081249999999997</v>
       </c>
@@ -6263,8 +5131,8 @@
         <v>4</v>
       </c>
       <c r="C36" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{4}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{4}</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -6292,7 +5160,7 @@
       </c>
       <c r="J36" s="1" t="str">
         <f t="shared" si="43"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K36" s="1" t="str">
         <f t="shared" si="43"/>
@@ -6376,7 +5244,7 @@
       </c>
       <c r="J37" s="1" t="str">
         <f t="shared" si="44"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="44"/>
@@ -6429,8 +5297,8 @@
         <v>4</v>
       </c>
       <c r="C38" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{4}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{4}</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -6458,7 +5326,7 @@
       </c>
       <c r="J38" s="1" t="str">
         <f t="shared" si="45"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="45"/>
@@ -6497,7 +5365,7 @@
       </c>
       <c r="T38" s="1" t="str">
         <f t="shared" ref="T38" si="46">_xlfn.CONCAT("['", C36, "' , '", C37, "']")</f>
-        <v>['\\mu_{4}' , 'err_{4}']</v>
+        <v>['\mu_{4}' , 'err_{4}']</v>
       </c>
       <c r="U38" s="1" t="str">
         <f t="shared" ref="U38" si="47">_xlfn.CONCAT("{", "}")</f>
@@ -6542,7 +5410,7 @@
       </c>
       <c r="J39" s="1" t="str">
         <f t="shared" si="48"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K39" s="1" t="str">
         <f t="shared" si="48"/>
@@ -6626,7 +5494,7 @@
       </c>
       <c r="J40" s="1" t="str">
         <f t="shared" si="49"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K40" s="1" t="str">
         <f t="shared" si="49"/>
@@ -6681,8 +5549,8 @@
         <v>4</v>
       </c>
       <c r="C41" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{4}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{4}</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -6710,7 +5578,7 @@
       </c>
       <c r="J41" s="1" t="str">
         <f t="shared" si="51"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K41" s="1" t="str">
         <f t="shared" si="51"/>
@@ -6793,7 +5661,7 @@
       </c>
       <c r="J42" s="1" t="str">
         <f t="shared" si="52"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K42" s="1" t="str">
         <f t="shared" si="52"/>
@@ -6832,7 +5700,7 @@
       </c>
       <c r="T42" s="1" t="str">
         <f t="shared" ref="T42" si="53">_xlfn.CONCAT("['", C35, "' , '", C36, "' , '", C39, "' , '", C40, "']")</f>
-        <v>['\\lambda_{4}' , '\\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
+        <v>['\lambda_{4}' , '\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
       </c>
       <c r="U42" s="1" t="str">
         <f t="shared" ref="U42:U45" si="54">_xlfn.CONCAT("{", "}")</f>
@@ -6877,7 +5745,7 @@
       </c>
       <c r="J43" s="1" t="str">
         <f t="shared" si="55"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K43" s="1" t="str">
         <f t="shared" si="55"/>
@@ -6916,7 +5784,7 @@
       </c>
       <c r="T43" s="1" t="str">
         <f t="shared" ref="T43" si="56">_xlfn.CONCAT("['", C35, "' , '", C36, "' , '", C39, "' , '", C40, "']")</f>
-        <v>['\\lambda_{4}' , '\\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
+        <v>['\lambda_{4}' , '\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
       </c>
       <c r="U43" s="1" t="str">
         <f t="shared" si="54"/>
@@ -6970,10 +5838,10 @@
       <c r="L44" s="1">
         <v>0</v>
       </c>
-      <c r="M44" s="11">
+      <c r="M44" s="10">
         <v>1.20527306967984E-2</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44" s="10">
         <v>1.20527306967984E-2</v>
       </c>
       <c r="O44" s="1" t="str">
@@ -6998,7 +5866,7 @@
       </c>
       <c r="T44" s="1" t="str">
         <f t="shared" ref="T44" si="58">_xlfn.CONCAT("['", C38, "' , '", C42, "']")</f>
-        <v>['\\chi_{4}' , 'L_{4}']</v>
+        <v>['\chi_{4}' , 'L_{4}']</v>
       </c>
       <c r="U44" s="1" t="str">
         <f t="shared" si="54"/>
@@ -7052,10 +5920,10 @@
       <c r="L45" s="1">
         <v>0</v>
       </c>
-      <c r="M45" s="11">
+      <c r="M45" s="10">
         <v>6.4971751412429297E-3</v>
       </c>
-      <c r="N45" s="11">
+      <c r="N45" s="10">
         <v>6.4971751412429297E-3</v>
       </c>
       <c r="O45" s="1" t="str">
@@ -7080,7 +5948,7 @@
       </c>
       <c r="T45" s="1" t="str">
         <f t="shared" ref="T45" si="60">_xlfn.CONCAT("['", C38, "' , '", C43, "']")</f>
-        <v>['\\chi_{4}' , 'Lq_{4}']</v>
+        <v>['\chi_{4}' , 'Lq_{4}']</v>
       </c>
       <c r="U45" s="1" t="str">
         <f t="shared" si="54"/>
@@ -7096,8 +5964,8 @@
         <v>5</v>
       </c>
       <c r="C46" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{5}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{5}</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -7125,7 +5993,7 @@
       </c>
       <c r="J46" s="1" t="str">
         <f t="shared" si="61"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K46" s="1" t="str">
         <f t="shared" si="61"/>
@@ -7134,7 +6002,7 @@
       <c r="L46" s="1">
         <v>0.1</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M46" s="10">
         <f>2*91.8145161290323</f>
         <v>183.6290322580646</v>
       </c>
@@ -7180,8 +6048,8 @@
         <v>5</v>
       </c>
       <c r="C47" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{5}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{5}</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -7209,7 +6077,7 @@
       </c>
       <c r="J47" s="1" t="str">
         <f t="shared" si="62"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K47" s="1" t="str">
         <f t="shared" si="62"/>
@@ -7293,7 +6161,7 @@
       </c>
       <c r="J48" s="1" t="str">
         <f t="shared" si="63"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K48" s="1" t="str">
         <f t="shared" si="63"/>
@@ -7347,8 +6215,8 @@
         <v>5</v>
       </c>
       <c r="C49" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{5}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{5}</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -7376,7 +6244,7 @@
       </c>
       <c r="J49" s="1" t="str">
         <f t="shared" si="64"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K49" s="1" t="str">
         <f t="shared" si="64"/>
@@ -7415,7 +6283,7 @@
       </c>
       <c r="T49" s="1" t="str">
         <f t="shared" ref="T49" si="65">_xlfn.CONCAT("['", C47, "' , '", C48, "']")</f>
-        <v>['\\mu_{5}' , 'err_{5}']</v>
+        <v>['\mu_{5}' , 'err_{5}']</v>
       </c>
       <c r="U49" s="1" t="str">
         <f t="shared" ref="U49" si="66">_xlfn.CONCAT("{", "}")</f>
@@ -7460,7 +6328,7 @@
       </c>
       <c r="J50" s="1" t="str">
         <f t="shared" si="67"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K50" s="1" t="str">
         <f t="shared" si="67"/>
@@ -7544,7 +6412,7 @@
       </c>
       <c r="J51" s="1" t="str">
         <f t="shared" si="68"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K51" s="1" t="str">
         <f t="shared" si="68"/>
@@ -7599,8 +6467,8 @@
         <v>5</v>
       </c>
       <c r="C52" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{5}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{5}</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -7628,7 +6496,7 @@
       </c>
       <c r="J52" s="1" t="str">
         <f t="shared" si="70"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K52" s="1" t="str">
         <f t="shared" si="70"/>
@@ -7711,7 +6579,7 @@
       </c>
       <c r="J53" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K53" s="1" t="str">
         <f t="shared" si="71"/>
@@ -7750,7 +6618,7 @@
       </c>
       <c r="T53" s="1" t="str">
         <f t="shared" ref="T53" si="72">_xlfn.CONCAT("['", C46, "' , '", C47, "' , '", C50, "' , '", C51, "']")</f>
-        <v>['\\lambda_{5}' , '\\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
+        <v>['\lambda_{5}' , '\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
       </c>
       <c r="U53" s="1" t="str">
         <f t="shared" ref="U53:U56" si="73">_xlfn.CONCAT("{", "}")</f>
@@ -7795,7 +6663,7 @@
       </c>
       <c r="J54" s="1" t="str">
         <f t="shared" si="74"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K54" s="1" t="str">
         <f t="shared" si="74"/>
@@ -7834,7 +6702,7 @@
       </c>
       <c r="T54" s="1" t="str">
         <f t="shared" ref="T54" si="75">_xlfn.CONCAT("['", C46, "' , '", C47, "' , '", C50, "' , '", C51, "']")</f>
-        <v>['\\lambda_{5}' , '\\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
+        <v>['\lambda_{5}' , '\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
       </c>
       <c r="U54" s="1" t="str">
         <f t="shared" si="73"/>
@@ -7888,10 +6756,10 @@
       <c r="L55" s="1">
         <v>0</v>
       </c>
-      <c r="M55" s="11">
+      <c r="M55" s="10">
         <v>2.2821385847059902E-3</v>
       </c>
-      <c r="N55" s="11">
+      <c r="N55" s="10">
         <v>2.2821385847059902E-3</v>
       </c>
       <c r="O55" s="1" t="str">
@@ -7916,7 +6784,7 @@
       </c>
       <c r="T55" s="1" t="str">
         <f t="shared" ref="T55" si="77">_xlfn.CONCAT("['", C49, "' , '", C53, "']")</f>
-        <v>['\\chi_{5}' , 'L_{5}']</v>
+        <v>['\chi_{5}' , 'L_{5}']</v>
       </c>
       <c r="U55" s="1" t="str">
         <f t="shared" si="73"/>
@@ -7970,10 +6838,10 @@
       <c r="L56" s="1">
         <v>0</v>
       </c>
-      <c r="M56" s="11">
+      <c r="M56" s="10">
         <v>3.95346131875801E-4</v>
       </c>
-      <c r="N56" s="11">
+      <c r="N56" s="10">
         <v>3.95346131875801E-4</v>
       </c>
       <c r="O56" s="1" t="str">
@@ -7998,7 +6866,7 @@
       </c>
       <c r="T56" s="1" t="str">
         <f t="shared" ref="T56" si="79">_xlfn.CONCAT("['", C49, "' , '", C54, "']")</f>
-        <v>['\\chi_{5}' , 'Lq_{5}']</v>
+        <v>['\chi_{5}' , 'Lq_{5}']</v>
       </c>
       <c r="U56" s="1" t="str">
         <f t="shared" si="73"/>
@@ -8014,8 +6882,8 @@
         <v>6</v>
       </c>
       <c r="C57" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{6}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{6}</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -8043,7 +6911,7 @@
       </c>
       <c r="J57" s="1" t="str">
         <f t="shared" si="80"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="80"/>
@@ -8052,11 +6920,11 @@
       <c r="L57" s="1">
         <v>0.1</v>
       </c>
-      <c r="M57" s="11">
+      <c r="M57" s="10">
         <f>2*104.131097560975</f>
         <v>208.26219512194999</v>
       </c>
-      <c r="N57" s="11">
+      <c r="N57" s="10">
         <v>104.13109756097499</v>
       </c>
       <c r="O57" s="1" t="str">
@@ -8097,8 +6965,8 @@
         <v>6</v>
       </c>
       <c r="C58" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{6}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{6}</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -8126,7 +6994,7 @@
       </c>
       <c r="J58" s="1" t="str">
         <f t="shared" si="81"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="81"/>
@@ -8210,7 +7078,7 @@
       </c>
       <c r="J59" s="1" t="str">
         <f t="shared" si="82"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="82"/>
@@ -8264,8 +7132,8 @@
         <v>6</v>
       </c>
       <c r="C60" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{6}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{6}</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -8293,7 +7161,7 @@
       </c>
       <c r="J60" s="1" t="str">
         <f t="shared" si="83"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="83"/>
@@ -8332,7 +7200,7 @@
       </c>
       <c r="T60" s="1" t="str">
         <f t="shared" ref="T60" si="84">_xlfn.CONCAT("['", C58, "' , '", C59, "']")</f>
-        <v>['\\mu_{6}' , 'err_{6}']</v>
+        <v>['\mu_{6}' , 'err_{6}']</v>
       </c>
       <c r="U60" s="1" t="str">
         <f t="shared" ref="U60" si="85">_xlfn.CONCAT("{", "}")</f>
@@ -8377,7 +7245,7 @@
       </c>
       <c r="J61" s="1" t="str">
         <f t="shared" si="86"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="86"/>
@@ -8461,7 +7329,7 @@
       </c>
       <c r="J62" s="1" t="str">
         <f t="shared" si="87"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K62" s="1" t="str">
         <f t="shared" si="87"/>
@@ -8516,8 +7384,8 @@
         <v>6</v>
       </c>
       <c r="C63" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{6}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{6}</v>
       </c>
       <c r="D63" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -8545,7 +7413,7 @@
       </c>
       <c r="J63" s="1" t="str">
         <f t="shared" si="89"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K63" s="1" t="str">
         <f t="shared" si="89"/>
@@ -8628,7 +7496,7 @@
       </c>
       <c r="J64" s="1" t="str">
         <f t="shared" si="90"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K64" s="1" t="str">
         <f t="shared" si="90"/>
@@ -8667,7 +7535,7 @@
       </c>
       <c r="T64" s="1" t="str">
         <f t="shared" ref="T64" si="91">_xlfn.CONCAT("['", C57, "' , '", C58, "' , '", C61, "' , '", C62, "']")</f>
-        <v>['\\lambda_{6}' , '\\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
+        <v>['\lambda_{6}' , '\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
       </c>
       <c r="U64" s="1" t="str">
         <f t="shared" ref="U64:U67" si="92">_xlfn.CONCAT("{", "}")</f>
@@ -8712,7 +7580,7 @@
       </c>
       <c r="J65" s="1" t="str">
         <f t="shared" si="93"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K65" s="1" t="str">
         <f t="shared" si="93"/>
@@ -8751,7 +7619,7 @@
       </c>
       <c r="T65" s="1" t="str">
         <f t="shared" ref="T65" si="94">_xlfn.CONCAT("['", C57, "' , '", C58, "' , '", C61, "' , '", C62, "']")</f>
-        <v>['\\lambda_{6}' , '\\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
+        <v>['\lambda_{6}' , '\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
       </c>
       <c r="U65" s="1" t="str">
         <f t="shared" si="92"/>
@@ -8805,10 +7673,10 @@
       <c r="L66" s="1">
         <v>0</v>
       </c>
-      <c r="M66" s="11">
+      <c r="M66" s="10">
         <v>2.1801262878032499E-2</v>
       </c>
-      <c r="N66" s="11">
+      <c r="N66" s="10">
         <v>2.1801262878032499E-2</v>
       </c>
       <c r="O66" s="1" t="str">
@@ -8833,7 +7701,7 @@
       </c>
       <c r="T66" s="1" t="str">
         <f t="shared" ref="T66" si="96">_xlfn.CONCAT("['", C60, "' , '", C64, "']")</f>
-        <v>['\\chi_{6}' , 'L_{6}']</v>
+        <v>['\chi_{6}' , 'L_{6}']</v>
       </c>
       <c r="U66" s="1" t="str">
         <f t="shared" si="92"/>
@@ -8887,10 +7755,10 @@
       <c r="L67" s="1">
         <v>0</v>
       </c>
-      <c r="M67" s="11">
+      <c r="M67" s="10">
         <v>1.5134596211365901E-2</v>
       </c>
-      <c r="N67" s="11">
+      <c r="N67" s="10">
         <v>1.5134596211365901E-2</v>
       </c>
       <c r="O67" s="1" t="str">
@@ -8915,7 +7783,7 @@
       </c>
       <c r="T67" s="1" t="str">
         <f t="shared" ref="T67" si="98">_xlfn.CONCAT("['", C60, "' , '", C65, "']")</f>
-        <v>['\\chi_{6}' , 'Lq_{6}']</v>
+        <v>['\chi_{6}' , 'Lq_{6}']</v>
       </c>
       <c r="U67" s="1" t="str">
         <f t="shared" si="92"/>
@@ -8931,8 +7799,8 @@
         <v>7</v>
       </c>
       <c r="C68" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{7}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{7}</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -8960,7 +7828,7 @@
       </c>
       <c r="J68" s="1" t="str">
         <f t="shared" si="99"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K68" s="1" t="str">
         <f t="shared" si="99"/>
@@ -8969,11 +7837,11 @@
       <c r="L68" s="1">
         <v>0.1</v>
       </c>
-      <c r="M68" s="11">
+      <c r="M68" s="10">
         <f>2*64.2740814606741</f>
         <v>128.54816292134819</v>
       </c>
-      <c r="N68" s="11">
+      <c r="N68" s="10">
         <v>64.274081460674097</v>
       </c>
       <c r="O68" s="1" t="str">
@@ -9014,8 +7882,8 @@
         <v>7</v>
       </c>
       <c r="C69" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{7}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{7}</v>
       </c>
       <c r="D69" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -9043,7 +7911,7 @@
       </c>
       <c r="J69" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K69" s="1" t="str">
         <f t="shared" si="100"/>
@@ -9127,7 +7995,7 @@
       </c>
       <c r="J70" s="1" t="str">
         <f t="shared" si="101"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K70" s="1" t="str">
         <f t="shared" si="101"/>
@@ -9181,8 +8049,8 @@
         <v>7</v>
       </c>
       <c r="C71" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{7}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{7}</v>
       </c>
       <c r="D71" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -9210,7 +8078,7 @@
       </c>
       <c r="J71" s="1" t="str">
         <f t="shared" si="102"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K71" s="1" t="str">
         <f t="shared" si="102"/>
@@ -9249,7 +8117,7 @@
       </c>
       <c r="T71" s="1" t="str">
         <f t="shared" ref="T71" si="103">_xlfn.CONCAT("['", C69, "' , '", C70, "']")</f>
-        <v>['\\mu_{7}' , 'err_{7}']</v>
+        <v>['\mu_{7}' , 'err_{7}']</v>
       </c>
       <c r="U71" s="1" t="str">
         <f t="shared" ref="U71" si="104">_xlfn.CONCAT("{", "}")</f>
@@ -9294,7 +8162,7 @@
       </c>
       <c r="J72" s="1" t="str">
         <f t="shared" si="105"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K72" s="1" t="str">
         <f t="shared" si="105"/>
@@ -9378,7 +8246,7 @@
       </c>
       <c r="J73" s="1" t="str">
         <f t="shared" si="106"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K73" s="1" t="str">
         <f t="shared" si="106"/>
@@ -9433,8 +8301,8 @@
         <v>7</v>
       </c>
       <c r="C74" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{7}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{7}</v>
       </c>
       <c r="D74" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -9462,7 +8330,7 @@
       </c>
       <c r="J74" s="1" t="str">
         <f t="shared" si="108"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K74" s="1" t="str">
         <f t="shared" si="108"/>
@@ -9545,7 +8413,7 @@
       </c>
       <c r="J75" s="1" t="str">
         <f t="shared" si="109"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K75" s="1" t="str">
         <f t="shared" si="109"/>
@@ -9584,7 +8452,7 @@
       </c>
       <c r="T75" s="1" t="str">
         <f t="shared" ref="T75" si="110">_xlfn.CONCAT("['", C68, "' , '", C69, "' , '", C72, "' , '", C73, "']")</f>
-        <v>['\\lambda_{7}' , '\\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
+        <v>['\lambda_{7}' , '\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
       </c>
       <c r="U75" s="1" t="str">
         <f t="shared" ref="U75:U78" si="111">_xlfn.CONCAT("{", "}")</f>
@@ -9629,7 +8497,7 @@
       </c>
       <c r="J76" s="1" t="str">
         <f t="shared" si="112"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K76" s="1" t="str">
         <f t="shared" si="112"/>
@@ -9668,7 +8536,7 @@
       </c>
       <c r="T76" s="1" t="str">
         <f t="shared" ref="T76" si="113">_xlfn.CONCAT("['", C68, "' , '", C69, "' , '", C72, "' , '", C73, "']")</f>
-        <v>['\\lambda_{7}' , '\\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
+        <v>['\lambda_{7}' , '\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
       </c>
       <c r="U76" s="1" t="str">
         <f t="shared" si="111"/>
@@ -9722,10 +8590,10 @@
       <c r="L77" s="1">
         <v>0</v>
       </c>
-      <c r="M77" s="11">
+      <c r="M77" s="10">
         <v>1.5730049237219199E-3</v>
       </c>
-      <c r="N77" s="11">
+      <c r="N77" s="10">
         <v>1.5730049237219199E-3</v>
       </c>
       <c r="O77" s="1" t="str">
@@ -9750,7 +8618,7 @@
       </c>
       <c r="T77" s="1" t="str">
         <f t="shared" ref="T77" si="115">_xlfn.CONCAT("['", C71, "' , '", C75, "']")</f>
-        <v>['\\chi_{7}' , 'L_{7}']</v>
+        <v>['\chi_{7}' , 'L_{7}']</v>
       </c>
       <c r="U77" s="1" t="str">
         <f t="shared" si="111"/>
@@ -9804,10 +8672,10 @@
       <c r="L78" s="1">
         <v>0</v>
       </c>
-      <c r="M78" s="11">
+      <c r="M78" s="10">
         <v>1.44433495150492E-4</v>
       </c>
-      <c r="N78" s="11">
+      <c r="N78" s="10">
         <v>1.44433495150492E-4</v>
       </c>
       <c r="O78" s="1" t="str">
@@ -9832,7 +8700,7 @@
       </c>
       <c r="T78" s="1" t="str">
         <f t="shared" ref="T78" si="120">_xlfn.CONCAT("['", C71, "' , '", C76, "']")</f>
-        <v>['\\chi_{7}' , 'Lq_{7}']</v>
+        <v>['\chi_{7}' , 'Lq_{7}']</v>
       </c>
       <c r="U78" s="1" t="str">
         <f t="shared" si="111"/>
@@ -9848,8 +8716,8 @@
         <v>8</v>
       </c>
       <c r="C79" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{8}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{8}</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -9877,7 +8745,7 @@
       </c>
       <c r="J79" s="1" t="str">
         <f t="shared" si="121"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K79" s="1" t="str">
         <f t="shared" si="121"/>
@@ -9886,11 +8754,11 @@
       <c r="L79" s="1">
         <v>0.1</v>
       </c>
-      <c r="M79" s="11">
+      <c r="M79" s="10">
         <f>2*59.5874296875</f>
         <v>119.174859375</v>
       </c>
-      <c r="N79" s="11">
+      <c r="N79" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>59.637429687499996</v>
       </c>
@@ -9932,8 +8800,8 @@
         <v>8</v>
       </c>
       <c r="C80" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{8}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{8}</v>
       </c>
       <c r="D80" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -9961,7 +8829,7 @@
       </c>
       <c r="J80" s="1" t="str">
         <f t="shared" si="122"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K80" s="1" t="str">
         <f t="shared" si="122"/>
@@ -10045,7 +8913,7 @@
       </c>
       <c r="J81" s="1" t="str">
         <f t="shared" si="123"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K81" s="1" t="str">
         <f t="shared" si="123"/>
@@ -10098,8 +8966,8 @@
         <v>8</v>
       </c>
       <c r="C82" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{8}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{8}</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -10127,7 +8995,7 @@
       </c>
       <c r="J82" s="1" t="str">
         <f t="shared" si="124"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K82" s="1" t="str">
         <f t="shared" si="124"/>
@@ -10166,7 +9034,7 @@
       </c>
       <c r="T82" s="1" t="str">
         <f t="shared" ref="T82" si="125">_xlfn.CONCAT("['", C80, "' , '", C81, "']")</f>
-        <v>['\\mu_{8}' , 'err_{8}']</v>
+        <v>['\mu_{8}' , 'err_{8}']</v>
       </c>
       <c r="U82" s="1" t="str">
         <f t="shared" ref="U82" si="126">_xlfn.CONCAT("{", "}")</f>
@@ -10211,7 +9079,7 @@
       </c>
       <c r="J83" s="1" t="str">
         <f t="shared" si="127"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K83" s="1" t="str">
         <f t="shared" si="127"/>
@@ -10295,7 +9163,7 @@
       </c>
       <c r="J84" s="1" t="str">
         <f t="shared" si="128"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K84" s="1" t="str">
         <f t="shared" si="128"/>
@@ -10350,8 +9218,8 @@
         <v>8</v>
       </c>
       <c r="C85" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{8}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{8}</v>
       </c>
       <c r="D85" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -10379,7 +9247,7 @@
       </c>
       <c r="J85" s="1" t="str">
         <f t="shared" si="130"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K85" s="1" t="str">
         <f t="shared" si="130"/>
@@ -10462,7 +9330,7 @@
       </c>
       <c r="J86" s="1" t="str">
         <f t="shared" si="131"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K86" s="1" t="str">
         <f t="shared" si="131"/>
@@ -10501,7 +9369,7 @@
       </c>
       <c r="T86" s="1" t="str">
         <f t="shared" ref="T86" si="132">_xlfn.CONCAT("['", C79, "' , '", C80, "' , '", C83, "' , '", C84, "']")</f>
-        <v>['\\lambda_{8}' , '\\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
+        <v>['\lambda_{8}' , '\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
       </c>
       <c r="U86" s="1" t="str">
         <f t="shared" ref="U86:U89" si="133">_xlfn.CONCAT("{", "}")</f>
@@ -10546,7 +9414,7 @@
       </c>
       <c r="J87" s="1" t="str">
         <f t="shared" si="134"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K87" s="1" t="str">
         <f t="shared" si="134"/>
@@ -10585,7 +9453,7 @@
       </c>
       <c r="T87" s="1" t="str">
         <f t="shared" ref="T87" si="135">_xlfn.CONCAT("['", C79, "' , '", C80, "' , '", C83, "' , '", C84, "']")</f>
-        <v>['\\lambda_{8}' , '\\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
+        <v>['\lambda_{8}' , '\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
       </c>
       <c r="U87" s="1" t="str">
         <f t="shared" si="133"/>
@@ -10667,7 +9535,7 @@
       </c>
       <c r="T88" s="1" t="str">
         <f t="shared" ref="T88" si="137">_xlfn.CONCAT("['", C82, "' , '", C86, "']")</f>
-        <v>['\\chi_{8}' , 'L_{8}']</v>
+        <v>['\chi_{8}' , 'L_{8}']</v>
       </c>
       <c r="U88" s="1" t="str">
         <f t="shared" si="133"/>
@@ -10749,7 +9617,7 @@
       </c>
       <c r="T89" s="1" t="str">
         <f t="shared" ref="T89" si="139">_xlfn.CONCAT("['", C82, "' , '", C87, "']")</f>
-        <v>['\\chi_{8}' , 'Lq_{8}']</v>
+        <v>['\chi_{8}' , 'Lq_{8}']</v>
       </c>
       <c r="U89" s="1" t="str">
         <f t="shared" si="133"/>
@@ -10765,8 +9633,8 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{9}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{9}</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -10794,7 +9662,7 @@
       </c>
       <c r="J90" s="1" t="str">
         <f t="shared" si="140"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K90" s="1" t="str">
         <f t="shared" si="140"/>
@@ -10803,11 +9671,11 @@
       <c r="L90" s="1">
         <v>0.1</v>
       </c>
-      <c r="M90" s="11">
+      <c r="M90" s="10">
         <f>2*38.7166666666666</f>
         <v>77.433333333333195</v>
       </c>
-      <c r="N90" s="11">
+      <c r="N90" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>38.766666666666595</v>
       </c>
@@ -10849,8 +9717,8 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{9}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{9}</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -10878,7 +9746,7 @@
       </c>
       <c r="J91" s="1" t="str">
         <f t="shared" si="141"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K91" s="1" t="str">
         <f t="shared" si="141"/>
@@ -10962,7 +9830,7 @@
       </c>
       <c r="J92" s="1" t="str">
         <f t="shared" si="142"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K92" s="1" t="str">
         <f t="shared" si="142"/>
@@ -11015,8 +9883,8 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{9}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{9}</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -11044,7 +9912,7 @@
       </c>
       <c r="J93" s="1" t="str">
         <f t="shared" si="143"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K93" s="1" t="str">
         <f t="shared" si="143"/>
@@ -11083,7 +9951,7 @@
       </c>
       <c r="T93" s="1" t="str">
         <f t="shared" ref="T93" si="144">_xlfn.CONCAT("['", C91, "' , '", C92, "']")</f>
-        <v>['\\mu_{9}' , 'err_{9}']</v>
+        <v>['\mu_{9}' , 'err_{9}']</v>
       </c>
       <c r="U93" s="1" t="str">
         <f t="shared" ref="U93" si="145">_xlfn.CONCAT("{", "}")</f>
@@ -11128,7 +9996,7 @@
       </c>
       <c r="J94" s="1" t="str">
         <f t="shared" si="146"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K94" s="1" t="str">
         <f t="shared" si="146"/>
@@ -11212,7 +10080,7 @@
       </c>
       <c r="J95" s="1" t="str">
         <f t="shared" si="147"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K95" s="1" t="str">
         <f t="shared" si="147"/>
@@ -11267,8 +10135,8 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{9}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{9}</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -11296,7 +10164,7 @@
       </c>
       <c r="J96" s="1" t="str">
         <f t="shared" si="149"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K96" s="1" t="str">
         <f t="shared" si="149"/>
@@ -11379,7 +10247,7 @@
       </c>
       <c r="J97" s="1" t="str">
         <f t="shared" si="150"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K97" s="1" t="str">
         <f t="shared" si="150"/>
@@ -11418,7 +10286,7 @@
       </c>
       <c r="T97" s="1" t="str">
         <f t="shared" ref="T97" si="151">_xlfn.CONCAT("['", C90, "' , '", C91, "' , '", C94, "' , '", C95, "']")</f>
-        <v>['\\lambda_{9}' , '\\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
+        <v>['\lambda_{9}' , '\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
       </c>
       <c r="U97" s="1" t="str">
         <f t="shared" ref="U97:U100" si="152">_xlfn.CONCAT("{", "}")</f>
@@ -11463,7 +10331,7 @@
       </c>
       <c r="J98" s="1" t="str">
         <f t="shared" si="154"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K98" s="1" t="str">
         <f t="shared" si="154"/>
@@ -11502,7 +10370,7 @@
       </c>
       <c r="T98" s="1" t="str">
         <f t="shared" ref="T98" si="155">_xlfn.CONCAT("['", C90, "' , '", C91, "' , '", C94, "' , '", C95, "']")</f>
-        <v>['\\lambda_{9}' , '\\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
+        <v>['\lambda_{9}' , '\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
       </c>
       <c r="U98" s="1" t="str">
         <f t="shared" si="152"/>
@@ -11556,10 +10424,10 @@
       <c r="L99" s="1">
         <v>0</v>
       </c>
-      <c r="M99" s="11">
+      <c r="M99" s="10">
         <v>6.6214680546859803E-4</v>
       </c>
-      <c r="N99" s="11">
+      <c r="N99" s="10">
         <v>6.6214680546859803E-4</v>
       </c>
       <c r="O99" s="1" t="str">
@@ -11584,7 +10452,7 @@
       </c>
       <c r="T99" s="1" t="str">
         <f t="shared" ref="T99" si="157">_xlfn.CONCAT("['", C93, "' , '", C97, "']")</f>
-        <v>['\\chi_{9}' , 'L_{9}']</v>
+        <v>['\chi_{9}' , 'L_{9}']</v>
       </c>
       <c r="U99" s="1" t="str">
         <f t="shared" si="152"/>
@@ -11638,10 +10506,10 @@
       <c r="L100" s="1">
         <v>0</v>
       </c>
-      <c r="M100" s="12">
+      <c r="M100" s="11">
         <v>2.9235413063535701E-5</v>
       </c>
-      <c r="N100" s="12">
+      <c r="N100" s="11">
         <v>2.9235413063535701E-5</v>
       </c>
       <c r="O100" s="1" t="str">
@@ -11666,7 +10534,7 @@
       </c>
       <c r="T100" s="1" t="str">
         <f t="shared" ref="T100" si="159">_xlfn.CONCAT("['", C93, "' , '", C98, "']")</f>
-        <v>['\\chi_{9}' , 'Lq_{9}']</v>
+        <v>['\chi_{9}' , 'Lq_{9}']</v>
       </c>
       <c r="U100" s="1" t="str">
         <f t="shared" si="152"/>
@@ -11682,8 +10550,8 @@
         <v>10</v>
       </c>
       <c r="C101" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{10}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{10}</v>
       </c>
       <c r="D101" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -11711,7 +10579,7 @@
       </c>
       <c r="J101" s="1" t="str">
         <f t="shared" si="160"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K101" s="1" t="str">
         <f t="shared" si="160"/>
@@ -11720,11 +10588,11 @@
       <c r="L101" s="1">
         <v>0.1</v>
       </c>
-      <c r="M101" s="11">
+      <c r="M101" s="10">
         <f>2*256.1625</f>
         <v>512.32500000000005</v>
       </c>
-      <c r="N101" s="11">
+      <c r="N101" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>256.21250000000003</v>
       </c>
@@ -11766,8 +10634,8 @@
         <v>10</v>
       </c>
       <c r="C102" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{10}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{10}</v>
       </c>
       <c r="D102" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -11795,7 +10663,7 @@
       </c>
       <c r="J102" s="1" t="str">
         <f t="shared" si="161"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K102" s="1" t="str">
         <f t="shared" si="161"/>
@@ -11879,7 +10747,7 @@
       </c>
       <c r="J103" s="1" t="str">
         <f t="shared" si="162"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K103" s="1" t="str">
         <f t="shared" si="162"/>
@@ -11932,8 +10800,8 @@
         <v>10</v>
       </c>
       <c r="C104" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{10}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{10}</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -11961,7 +10829,7 @@
       </c>
       <c r="J104" s="1" t="str">
         <f t="shared" si="163"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K104" s="1" t="str">
         <f t="shared" si="163"/>
@@ -12000,7 +10868,7 @@
       </c>
       <c r="T104" s="1" t="str">
         <f t="shared" ref="T104" si="164">_xlfn.CONCAT("['", C102, "' , '", C103, "']")</f>
-        <v>['\\mu_{10}' , 'err_{10}']</v>
+        <v>['\mu_{10}' , 'err_{10}']</v>
       </c>
       <c r="U104" s="1" t="str">
         <f t="shared" ref="U104" si="165">_xlfn.CONCAT("{", "}")</f>
@@ -12045,7 +10913,7 @@
       </c>
       <c r="J105" s="1" t="str">
         <f t="shared" si="166"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K105" s="1" t="str">
         <f t="shared" si="166"/>
@@ -12129,7 +10997,7 @@
       </c>
       <c r="J106" s="1" t="str">
         <f t="shared" si="167"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K106" s="1" t="str">
         <f t="shared" si="167"/>
@@ -12184,8 +11052,8 @@
         <v>10</v>
       </c>
       <c r="C107" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{10}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{10}</v>
       </c>
       <c r="D107" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -12213,7 +11081,7 @@
       </c>
       <c r="J107" s="1" t="str">
         <f t="shared" si="169"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K107" s="1" t="str">
         <f t="shared" si="169"/>
@@ -12296,7 +11164,7 @@
       </c>
       <c r="J108" s="1" t="str">
         <f t="shared" si="170"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K108" s="1" t="str">
         <f t="shared" si="170"/>
@@ -12335,7 +11203,7 @@
       </c>
       <c r="T108" s="1" t="str">
         <f t="shared" ref="T108" si="171">_xlfn.CONCAT("['", C101, "' , '", C102, "' , '", C105, "' , '", C106, "']")</f>
-        <v>['\\lambda_{10}' , '\\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
+        <v>['\lambda_{10}' , '\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
       </c>
       <c r="U108" s="1" t="str">
         <f t="shared" ref="U108:U111" si="172">_xlfn.CONCAT("{", "}")</f>
@@ -12380,7 +11248,7 @@
       </c>
       <c r="J109" s="1" t="str">
         <f t="shared" si="173"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K109" s="1" t="str">
         <f t="shared" si="173"/>
@@ -12419,7 +11287,7 @@
       </c>
       <c r="T109" s="1" t="str">
         <f t="shared" ref="T109" si="174">_xlfn.CONCAT("['", C101, "' , '", C102, "' , '", C105, "' , '", C106, "']")</f>
-        <v>['\\lambda_{10}' , '\\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
+        <v>['\lambda_{10}' , '\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
       </c>
       <c r="U109" s="1" t="str">
         <f t="shared" si="172"/>
@@ -12473,10 +11341,10 @@
       <c r="L110" s="1">
         <v>0</v>
       </c>
-      <c r="M110" s="11">
+      <c r="M110" s="10">
         <v>2.2530768580843199E-3</v>
       </c>
-      <c r="N110" s="11">
+      <c r="N110" s="10">
         <v>2.2530768580843199E-3</v>
       </c>
       <c r="O110" s="1" t="str">
@@ -12501,7 +11369,7 @@
       </c>
       <c r="T110" s="1" t="str">
         <f t="shared" ref="T110" si="176">_xlfn.CONCAT("['", C104, "' , '", C108, "']")</f>
-        <v>['\\chi_{10}' , 'L_{10}']</v>
+        <v>['\chi_{10}' , 'L_{10}']</v>
       </c>
       <c r="U110" s="1" t="str">
         <f t="shared" si="172"/>
@@ -12555,10 +11423,10 @@
       <c r="L111" s="1">
         <v>0</v>
       </c>
-      <c r="M111" s="11">
+      <c r="M111" s="10">
         <v>8.2450542951289195E-4</v>
       </c>
-      <c r="N111" s="11">
+      <c r="N111" s="10">
         <v>8.2450542951289195E-4</v>
       </c>
       <c r="O111" s="1" t="str">
@@ -12583,7 +11451,7 @@
       </c>
       <c r="T111" s="1" t="str">
         <f t="shared" ref="T111" si="178">_xlfn.CONCAT("['", C104, "' , '", C109, "']")</f>
-        <v>['\\chi_{10}' , 'Lq_{10}']</v>
+        <v>['\chi_{10}' , 'Lq_{10}']</v>
       </c>
       <c r="U111" s="1" t="str">
         <f t="shared" si="172"/>
@@ -12599,8 +11467,8 @@
         <v>11</v>
       </c>
       <c r="C112" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{11}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{11}</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -12628,7 +11496,7 @@
       </c>
       <c r="J112" s="1" t="str">
         <f t="shared" si="179"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K112" s="1" t="str">
         <f t="shared" si="179"/>
@@ -12637,11 +11505,11 @@
       <c r="L112" s="1">
         <v>0.1</v>
       </c>
-      <c r="M112" s="11">
+      <c r="M112" s="10">
         <f>2*177.965526315789</f>
         <v>355.93105263157798</v>
       </c>
-      <c r="N112" s="11">
+      <c r="N112" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>178.015526315789</v>
       </c>
@@ -12683,8 +11551,8 @@
         <v>11</v>
       </c>
       <c r="C113" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{11}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{11}</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -12712,7 +11580,7 @@
       </c>
       <c r="J113" s="1" t="str">
         <f t="shared" si="180"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K113" s="1" t="str">
         <f t="shared" si="180"/>
@@ -12796,7 +11664,7 @@
       </c>
       <c r="J114" s="1" t="str">
         <f t="shared" si="181"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K114" s="1" t="str">
         <f t="shared" si="181"/>
@@ -12849,8 +11717,8 @@
         <v>11</v>
       </c>
       <c r="C115" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{11}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{11}</v>
       </c>
       <c r="D115" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -12878,7 +11746,7 @@
       </c>
       <c r="J115" s="1" t="str">
         <f t="shared" si="182"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K115" s="1" t="str">
         <f t="shared" si="182"/>
@@ -12917,7 +11785,7 @@
       </c>
       <c r="T115" s="1" t="str">
         <f t="shared" ref="T115" si="183">_xlfn.CONCAT("['", C113, "' , '", C114, "']")</f>
-        <v>['\\mu_{11}' , 'err_{11}']</v>
+        <v>['\mu_{11}' , 'err_{11}']</v>
       </c>
       <c r="U115" s="1" t="str">
         <f t="shared" ref="U115" si="184">_xlfn.CONCAT("{", "}")</f>
@@ -12962,7 +11830,7 @@
       </c>
       <c r="J116" s="1" t="str">
         <f t="shared" si="185"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K116" s="1" t="str">
         <f t="shared" si="185"/>
@@ -13046,7 +11914,7 @@
       </c>
       <c r="J117" s="1" t="str">
         <f t="shared" si="187"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K117" s="1" t="str">
         <f t="shared" si="187"/>
@@ -13101,8 +11969,8 @@
         <v>11</v>
       </c>
       <c r="C118" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{11}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{11}</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -13130,7 +11998,7 @@
       </c>
       <c r="J118" s="1" t="str">
         <f t="shared" si="189"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K118" s="1" t="str">
         <f t="shared" si="189"/>
@@ -13213,7 +12081,7 @@
       </c>
       <c r="J119" s="1" t="str">
         <f t="shared" si="190"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K119" s="1" t="str">
         <f t="shared" si="190"/>
@@ -13252,7 +12120,7 @@
       </c>
       <c r="T119" s="1" t="str">
         <f t="shared" ref="T119" si="191">_xlfn.CONCAT("['", C112, "' , '", C113, "' , '", C116, "' , '", C117, "']")</f>
-        <v>['\\lambda_{11}' , '\\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
+        <v>['\lambda_{11}' , '\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
       </c>
       <c r="U119" s="1" t="str">
         <f t="shared" ref="U119:U122" si="192">_xlfn.CONCAT("{", "}")</f>
@@ -13297,7 +12165,7 @@
       </c>
       <c r="J120" s="1" t="str">
         <f t="shared" si="193"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K120" s="1" t="str">
         <f t="shared" si="193"/>
@@ -13336,7 +12204,7 @@
       </c>
       <c r="T120" s="1" t="str">
         <f t="shared" ref="T120" si="194">_xlfn.CONCAT("['", C112, "' , '", C113, "' , '", C116, "' , '", C117, "']")</f>
-        <v>['\\lambda_{11}' , '\\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
+        <v>['\lambda_{11}' , '\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
       </c>
       <c r="U120" s="1" t="str">
         <f t="shared" si="192"/>
@@ -13418,7 +12286,7 @@
       </c>
       <c r="T121" s="1" t="str">
         <f t="shared" ref="T121" si="196">_xlfn.CONCAT("['", C115, "' , '", C119, "']")</f>
-        <v>['\\chi_{11}' , 'L_{11}']</v>
+        <v>['\chi_{11}' , 'L_{11}']</v>
       </c>
       <c r="U121" s="1" t="str">
         <f t="shared" si="192"/>
@@ -13472,10 +12340,10 @@
       <c r="L122" s="1">
         <v>0</v>
       </c>
-      <c r="M122" s="11">
+      <c r="M122" s="10">
         <v>8.6974113179947199E-4</v>
       </c>
-      <c r="N122" s="11">
+      <c r="N122" s="10">
         <v>8.6974113179947199E-4</v>
       </c>
       <c r="O122" s="1" t="str">
@@ -13500,7 +12368,7 @@
       </c>
       <c r="T122" s="1" t="str">
         <f t="shared" ref="T122" si="198">_xlfn.CONCAT("['", C115, "' , '", C120, "']")</f>
-        <v>['\\chi_{11}' , 'Lq_{11}']</v>
+        <v>['\chi_{11}' , 'Lq_{11}']</v>
       </c>
       <c r="U122" s="1" t="str">
         <f t="shared" si="192"/>
@@ -13516,8 +12384,8 @@
         <v>12</v>
       </c>
       <c r="C123" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{12}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{12}</v>
       </c>
       <c r="D123" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -13545,7 +12413,7 @@
       </c>
       <c r="J123" s="1" t="str">
         <f t="shared" si="199"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K123" s="1" t="str">
         <f t="shared" si="199"/>
@@ -13554,11 +12422,11 @@
       <c r="L123" s="1">
         <v>0.1</v>
       </c>
-      <c r="M123" s="11">
+      <c r="M123" s="10">
         <f>2*171.6117975</f>
         <v>343.22359499999999</v>
       </c>
-      <c r="N123" s="11">
+      <c r="N123" s="10">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
         <v>171.66179750000001</v>
       </c>
@@ -13600,8 +12468,8 @@
         <v>12</v>
       </c>
       <c r="C124" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{12}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{12}</v>
       </c>
       <c r="D124" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -13629,7 +12497,7 @@
       </c>
       <c r="J124" s="1" t="str">
         <f t="shared" si="200"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K124" s="1" t="str">
         <f t="shared" si="200"/>
@@ -13713,7 +12581,7 @@
       </c>
       <c r="J125" s="1" t="str">
         <f t="shared" si="201"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K125" s="1" t="str">
         <f t="shared" si="201"/>
@@ -13766,8 +12634,8 @@
         <v>12</v>
       </c>
       <c r="C126" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{12}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{12}</v>
       </c>
       <c r="D126" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -13795,7 +12663,7 @@
       </c>
       <c r="J126" s="1" t="str">
         <f t="shared" si="202"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K126" s="1" t="str">
         <f t="shared" si="202"/>
@@ -13834,7 +12702,7 @@
       </c>
       <c r="T126" s="1" t="str">
         <f t="shared" ref="T126" si="203">_xlfn.CONCAT("['", C124, "' , '", C125, "']")</f>
-        <v>['\\mu_{12}' , 'err_{12}']</v>
+        <v>['\mu_{12}' , 'err_{12}']</v>
       </c>
       <c r="U126" s="1" t="str">
         <f t="shared" ref="U126" si="204">_xlfn.CONCAT("{", "}")</f>
@@ -13879,7 +12747,7 @@
       </c>
       <c r="J127" s="1" t="str">
         <f t="shared" si="205"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K127" s="1" t="str">
         <f t="shared" si="205"/>
@@ -13963,7 +12831,7 @@
       </c>
       <c r="J128" s="1" t="str">
         <f t="shared" si="206"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K128" s="1" t="str">
         <f t="shared" si="206"/>
@@ -14018,8 +12886,8 @@
         <v>12</v>
       </c>
       <c r="C129" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{12}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{12}</v>
       </c>
       <c r="D129" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -14047,7 +12915,7 @@
       </c>
       <c r="J129" s="1" t="str">
         <f t="shared" si="208"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K129" s="1" t="str">
         <f t="shared" si="208"/>
@@ -14130,7 +12998,7 @@
       </c>
       <c r="J130" s="1" t="str">
         <f t="shared" si="209"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K130" s="1" t="str">
         <f t="shared" si="209"/>
@@ -14169,7 +13037,7 @@
       </c>
       <c r="T130" s="1" t="str">
         <f t="shared" ref="T130" si="210">_xlfn.CONCAT("['", C123, "' , '", C124, "' , '", C127, "' , '", C128, "']")</f>
-        <v>['\\lambda_{12}' , '\\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
+        <v>['\lambda_{12}' , '\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
       </c>
       <c r="U130" s="1" t="str">
         <f t="shared" ref="U130:U133" si="211">_xlfn.CONCAT("{", "}")</f>
@@ -14214,7 +13082,7 @@
       </c>
       <c r="J131" s="1" t="str">
         <f t="shared" si="212"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K131" s="1" t="str">
         <f t="shared" si="212"/>
@@ -14253,7 +13121,7 @@
       </c>
       <c r="T131" s="1" t="str">
         <f t="shared" ref="T131" si="213">_xlfn.CONCAT("['", C123, "' , '", C124, "' , '", C127, "' , '", C128, "']")</f>
-        <v>['\\lambda_{12}' , '\\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
+        <v>['\lambda_{12}' , '\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
       </c>
       <c r="U131" s="1" t="str">
         <f t="shared" si="211"/>
@@ -14307,10 +13175,10 @@
       <c r="L132" s="1">
         <v>0</v>
       </c>
-      <c r="M132" s="11">
+      <c r="M132" s="10">
         <v>1.89254793212382E-3</v>
       </c>
-      <c r="N132" s="11">
+      <c r="N132" s="10">
         <v>1.89254793212382E-3</v>
       </c>
       <c r="O132" s="1" t="str">
@@ -14335,7 +13203,7 @@
       </c>
       <c r="T132" s="1" t="str">
         <f t="shared" ref="T132" si="215">_xlfn.CONCAT("['", C126, "' , '", C130, "']")</f>
-        <v>['\\chi_{12}' , 'L_{12}']</v>
+        <v>['\chi_{12}' , 'L_{12}']</v>
       </c>
       <c r="U132" s="1" t="str">
         <f t="shared" si="211"/>
@@ -14389,10 +13257,10 @@
       <c r="L133" s="1">
         <v>0</v>
       </c>
-      <c r="M133" s="11">
+      <c r="M133" s="10">
         <v>4.6397650355239602E-4</v>
       </c>
-      <c r="N133" s="11">
+      <c r="N133" s="10">
         <v>4.6397650355239602E-4</v>
       </c>
       <c r="O133" s="1" t="str">
@@ -14417,7 +13285,7 @@
       </c>
       <c r="T133" s="1" t="str">
         <f t="shared" ref="T133" si="217">_xlfn.CONCAT("['", C126, "' , '", C131, "']")</f>
-        <v>['\\chi_{12}' , 'Lq_{12}']</v>
+        <v>['\chi_{12}' , 'Lq_{12}']</v>
       </c>
       <c r="U133" s="1" t="str">
         <f t="shared" si="211"/>
@@ -14433,8 +13301,8 @@
         <v>13</v>
       </c>
       <c r="C134" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{13}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{13}</v>
       </c>
       <c r="D134" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table1[[#This Row],[dm]])</f>
@@ -14462,7 +13330,7 @@
       </c>
       <c r="J134" s="1" t="str">
         <f t="shared" si="218"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K134" s="1" t="str">
         <f t="shared" si="218"/>
@@ -14471,7 +13339,7 @@
       <c r="L134" s="1">
         <v>0.1</v>
       </c>
-      <c r="M134" s="11">
+      <c r="M134" s="10">
         <f>2*169.067249999999</f>
         <v>338.13449999999801</v>
       </c>
@@ -14517,8 +13385,8 @@
         <v>13</v>
       </c>
       <c r="C135" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{13}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\mu_{13}</v>
       </c>
       <c r="D135" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table1[[#This Row],[dm]])</f>
@@ -14546,7 +13414,7 @@
       </c>
       <c r="J135" s="1" t="str">
         <f t="shared" si="219"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K135" s="1" t="str">
         <f t="shared" si="219"/>
@@ -14630,7 +13498,7 @@
       </c>
       <c r="J136" s="1" t="str">
         <f t="shared" si="220"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K136" s="1" t="str">
         <f t="shared" si="220"/>
@@ -14683,8 +13551,8 @@
         <v>13</v>
       </c>
       <c r="C137" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table1[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{13}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table1[[#This Row],[dm]], "}")</f>
+        <v>\chi_{13}</v>
       </c>
       <c r="D137" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table1[[#This Row],[dm]])</f>
@@ -14712,7 +13580,7 @@
       </c>
       <c r="J137" s="1" t="str">
         <f t="shared" si="221"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K137" s="1" t="str">
         <f t="shared" si="221"/>
@@ -14751,7 +13619,7 @@
       </c>
       <c r="T137" s="1" t="str">
         <f t="shared" ref="T137" si="222">_xlfn.CONCAT("['", C135, "' , '", C136, "']")</f>
-        <v>['\\mu_{13}' , 'err_{13}']</v>
+        <v>['\mu_{13}' , 'err_{13}']</v>
       </c>
       <c r="U137" s="1" t="str">
         <f t="shared" ref="U137" si="223">_xlfn.CONCAT("{", "}")</f>
@@ -14796,7 +13664,7 @@
       </c>
       <c r="J138" s="1" t="str">
         <f t="shared" si="224"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K138" s="1" t="str">
         <f t="shared" si="224"/>
@@ -14880,7 +13748,7 @@
       </c>
       <c r="J139" s="1" t="str">
         <f t="shared" si="225"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K139" s="1" t="str">
         <f t="shared" si="225"/>
@@ -14935,8 +13803,8 @@
         <v>13</v>
       </c>
       <c r="C140" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table1[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{13}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table1[[#This Row],[dm]],"}")</f>
+        <v>\delta_{13}</v>
       </c>
       <c r="D140" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table1[[#This Row],[dm]])</f>
@@ -14964,7 +13832,7 @@
       </c>
       <c r="J140" s="1" t="str">
         <f t="shared" si="227"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K140" s="1" t="str">
         <f t="shared" si="227"/>
@@ -15047,7 +13915,7 @@
       </c>
       <c r="J141" s="1" t="str">
         <f t="shared" si="228"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K141" s="1" t="str">
         <f t="shared" si="228"/>
@@ -15086,7 +13954,7 @@
       </c>
       <c r="T141" s="1" t="str">
         <f t="shared" ref="T141" si="229">_xlfn.CONCAT("['", C134, "' , '", C135, "' , '", C138, "' , '", C139, "']")</f>
-        <v>['\\lambda_{13}' , '\\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
+        <v>['\lambda_{13}' , '\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
       </c>
       <c r="U141" s="1" t="str">
         <f t="shared" ref="U141:U144" si="230">_xlfn.CONCAT("{", "}")</f>
@@ -15131,7 +13999,7 @@
       </c>
       <c r="J142" s="1" t="str">
         <f t="shared" si="232"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K142" s="1" t="str">
         <f t="shared" si="232"/>
@@ -15170,7 +14038,7 @@
       </c>
       <c r="T142" s="1" t="str">
         <f t="shared" ref="T142" si="234">_xlfn.CONCAT("['", C134, "' , '", C135, "' , '", C138, "' , '", C139, "']")</f>
-        <v>['\\lambda_{13}' , '\\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
+        <v>['\lambda_{13}' , '\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
       </c>
       <c r="U142" s="1" t="str">
         <f t="shared" si="230"/>
@@ -15224,10 +14092,10 @@
       <c r="L143" s="1">
         <v>0</v>
       </c>
-      <c r="M143" s="11">
+      <c r="M143" s="10">
         <v>1.8834777097476E-3</v>
       </c>
-      <c r="N143" s="11">
+      <c r="N143" s="10">
         <v>1.8834777097476E-3</v>
       </c>
       <c r="O143" s="1" t="str">
@@ -15252,7 +14120,7 @@
       </c>
       <c r="T143" s="1" t="str">
         <f t="shared" ref="T143" si="236">_xlfn.CONCAT("['", C137, "' , '", C141, "']")</f>
-        <v>['\\chi_{13}' , 'L_{13}']</v>
+        <v>['\chi_{13}' , 'L_{13}']</v>
       </c>
       <c r="U143" s="1" t="str">
         <f t="shared" si="230"/>
@@ -15306,10 +14174,10 @@
       <c r="L144" s="1">
         <v>0</v>
       </c>
-      <c r="M144" s="11">
+      <c r="M144" s="10">
         <v>4.5490628117617998E-4</v>
       </c>
-      <c r="N144" s="11">
+      <c r="N144" s="10">
         <v>4.5490628117617998E-4</v>
       </c>
       <c r="O144" s="1" t="str">
@@ -15334,7 +14202,7 @@
       </c>
       <c r="T144" s="1" t="str">
         <f t="shared" ref="T144" si="238">_xlfn.CONCAT("['", C137, "' , '", C142, "']")</f>
-        <v>['\\chi_{13}' , 'Lq_{13}']</v>
+        <v>['\chi_{13}' , 'Lq_{13}']</v>
       </c>
       <c r="U144" s="1" t="str">
         <f t="shared" si="230"/>
@@ -15451,15 +14319,15 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{1}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{1}</v>
       </c>
       <c r="D2" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
         <v>lambda_tas_1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " arrival rate")</f>
@@ -15476,7 +14344,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>4</v>
@@ -15528,15 +14396,15 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{1}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{1}</v>
       </c>
       <c r="D3" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
         <v>mu_tas_1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " service rate")</f>
@@ -15553,7 +14421,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>4</v>
@@ -15613,7 +14481,7 @@
         <v>err_tas_1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " error probability")</f>
@@ -15630,7 +14498,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>31</v>
@@ -15681,15 +14549,15 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{1}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{1}</v>
       </c>
       <c r="D5" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
         <v>chi_tas_1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " departure rate")</f>
@@ -15706,7 +14574,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>4</v>
@@ -15743,7 +14611,7 @@
       </c>
       <c r="T5" s="1" t="str">
         <f>_xlfn.CONCAT("['", C3, "' , '", C4, "']")</f>
-        <v>['\\mu_{1}' , 'err_{1}']</v>
+        <v>['\mu_{1}' , 'err_{1}']</v>
       </c>
       <c r="U5" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -15766,7 +14634,7 @@
         <v>c_tas_1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " resourses")</f>
@@ -15783,7 +14651,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>7</v>
@@ -15843,7 +14711,7 @@
         <v>K_tas_1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " q-capacity")</f>
@@ -15860,7 +14728,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>7</v>
@@ -15912,15 +14780,15 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{1}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{1}</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
         <v>delta_tas_1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " req data density")</f>
@@ -15937,7 +14805,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -15995,7 +14863,7 @@
         <v>L_tas_1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " mean processing requests")</f>
@@ -16012,7 +14880,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>7</v>
@@ -16049,7 +14917,7 @@
       </c>
       <c r="T9" s="1" t="str">
         <f>_xlfn.CONCAT("['", C2, "' , '", C3, "' , '", C6, "' , '", C7, "']")</f>
-        <v>['\\lambda_{1}' , '\\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
+        <v>['\lambda_{1}' , '\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
       </c>
       <c r="U9" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -16072,7 +14940,7 @@
         <v>Lq_tas_1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " mean in memory requests")</f>
@@ -16089,7 +14957,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>7</v>
@@ -16126,7 +14994,7 @@
       </c>
       <c r="T10" s="1" t="str">
         <f>_xlfn.CONCAT("['", C2, "' , '", C3, "' , '", C6, "' , '", C7, "']")</f>
-        <v>['\\lambda_{1}' , '\\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
+        <v>['\lambda_{1}' , '\mu_{1}' , 'c_{1}' , 'K_{1}']</v>
       </c>
       <c r="U10" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -16149,7 +15017,7 @@
         <v>W_tas_1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " mean time to answer")</f>
@@ -16201,7 +15069,7 @@
       </c>
       <c r="T11" s="1" t="str">
         <f>_xlfn.CONCAT("['", C5, "' , '", C9, "']")</f>
-        <v>['\\chi_{1}' , 'L_{1}']</v>
+        <v>['\chi_{1}' , 'L_{1}']</v>
       </c>
       <c r="U11" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -16224,7 +15092,7 @@
         <v>Wq_tas_1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table16[[#This Row],[dm]], " mean time in buffer")</f>
@@ -16276,7 +15144,7 @@
       </c>
       <c r="T12" s="1" t="str">
         <f>_xlfn.CONCAT("['", C5, "' , '", C10, "']")</f>
-        <v>['\\chi_{1}' , 'Lq_{1}']</v>
+        <v>['\chi_{1}' , 'Lq_{1}']</v>
       </c>
       <c r="U12" s="1" t="str">
         <f>_xlfn.CONCAT("{", "}")</f>
@@ -16292,8 +15160,8 @@
         <v>2</v>
       </c>
       <c r="C13" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{2}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{2}</v>
       </c>
       <c r="D13" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -16321,7 +15189,7 @@
       </c>
       <c r="J13" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K13" s="1" t="str">
         <f t="shared" si="1"/>
@@ -16376,8 +15244,8 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{2}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{2}</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -16405,7 +15273,7 @@
       </c>
       <c r="J14" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K14" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16489,7 +15357,7 @@
       </c>
       <c r="J15" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K15" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16543,8 +15411,8 @@
         <v>2</v>
       </c>
       <c r="C16" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{2}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{2}</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -16572,7 +15440,7 @@
       </c>
       <c r="J16" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K16" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16611,7 +15479,7 @@
       </c>
       <c r="T16" s="1" t="str">
         <f t="shared" ref="T16" si="6">_xlfn.CONCAT("['", C14, "' , '", C15, "']")</f>
-        <v>['\\mu_{2}' , 'err_{2}']</v>
+        <v>['\mu_{2}' , 'err_{2}']</v>
       </c>
       <c r="U16" s="1" t="str">
         <f t="shared" ref="U16" si="7">_xlfn.CONCAT("{", "}")</f>
@@ -16656,7 +15524,7 @@
       </c>
       <c r="J17" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K17" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16740,7 +15608,7 @@
       </c>
       <c r="J18" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K18" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16795,8 +15663,8 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{2}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{2}</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -16824,7 +15692,7 @@
       </c>
       <c r="J19" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K19" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16906,7 +15774,7 @@
       </c>
       <c r="J20" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="4"/>
@@ -16945,7 +15813,7 @@
       </c>
       <c r="T20" s="1" t="str">
         <f t="shared" ref="T20" si="9">_xlfn.CONCAT("['", C13, "' , '", C14, "' , '", C17, "' , '", C18, "']")</f>
-        <v>['\\lambda_{2}' , '\\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
+        <v>['\lambda_{2}' , '\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
       </c>
       <c r="U20" s="1" t="str">
         <f t="shared" ref="U20:U23" si="10">_xlfn.CONCAT("{", "}")</f>
@@ -16990,7 +15858,7 @@
       </c>
       <c r="J21" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K21" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17029,7 +15897,7 @@
       </c>
       <c r="T21" s="1" t="str">
         <f t="shared" ref="T21" si="11">_xlfn.CONCAT("['", C13, "' , '", C14, "' , '", C17, "' , '", C18, "']")</f>
-        <v>['\\lambda_{2}' , '\\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
+        <v>['\lambda_{2}' , '\mu_{2}' , 'c_{2}' , 'K_{2}']</v>
       </c>
       <c r="U21" s="1" t="str">
         <f t="shared" si="10"/>
@@ -17111,7 +15979,7 @@
       </c>
       <c r="T22" s="1" t="str">
         <f t="shared" ref="T22" si="12">_xlfn.CONCAT("['", C16, "' , '", C20, "']")</f>
-        <v>['\\chi_{2}' , 'L_{2}']</v>
+        <v>['\chi_{2}' , 'L_{2}']</v>
       </c>
       <c r="U22" s="1" t="str">
         <f t="shared" si="10"/>
@@ -17193,7 +16061,7 @@
       </c>
       <c r="T23" s="1" t="str">
         <f t="shared" ref="T23" si="13">_xlfn.CONCAT("['", C16, "' , '", C21, "']")</f>
-        <v>['\\chi_{2}' , 'Lq_{2}']</v>
+        <v>['\chi_{2}' , 'Lq_{2}']</v>
       </c>
       <c r="U23" s="1" t="str">
         <f t="shared" si="10"/>
@@ -17209,8 +16077,8 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{3}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{3}</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -17238,7 +16106,7 @@
       </c>
       <c r="J24" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K24" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17293,8 +16161,8 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{3}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{3}</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -17322,7 +16190,7 @@
       </c>
       <c r="J25" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K25" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17406,7 +16274,7 @@
       </c>
       <c r="J26" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17459,8 +16327,8 @@
         <v>3</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{3}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{3}</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -17488,7 +16356,7 @@
       </c>
       <c r="J27" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K27" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17527,7 +16395,7 @@
       </c>
       <c r="T27" s="1" t="str">
         <f t="shared" ref="T27" si="14">_xlfn.CONCAT("['", C25, "' , '", C26, "']")</f>
-        <v>['\\mu_{3}' , 'err_{3}']</v>
+        <v>['\mu_{3}' , 'err_{3}']</v>
       </c>
       <c r="U27" s="1" t="str">
         <f t="shared" ref="U27" si="15">_xlfn.CONCAT("{", "}")</f>
@@ -17572,7 +16440,7 @@
       </c>
       <c r="J28" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K28" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17656,7 +16524,7 @@
       </c>
       <c r="J29" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="4"/>
@@ -17711,8 +16579,8 @@
         <v>3</v>
       </c>
       <c r="C30" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{3}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{3}</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -17740,7 +16608,7 @@
       </c>
       <c r="J30" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="17"/>
@@ -17822,7 +16690,7 @@
       </c>
       <c r="J31" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K31" s="1" t="str">
         <f t="shared" si="17"/>
@@ -17861,7 +16729,7 @@
       </c>
       <c r="T31" s="1" t="str">
         <f t="shared" ref="T31" si="18">_xlfn.CONCAT("['", C24, "' , '", C25, "' , '", C28, "' , '", C29, "']")</f>
-        <v>['\\lambda_{3}' , '\\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
+        <v>['\lambda_{3}' , '\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
       </c>
       <c r="U31" s="1" t="str">
         <f t="shared" ref="U31:U34" si="19">_xlfn.CONCAT("{", "}")</f>
@@ -17906,7 +16774,7 @@
       </c>
       <c r="J32" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K32" s="1" t="str">
         <f t="shared" si="17"/>
@@ -17945,7 +16813,7 @@
       </c>
       <c r="T32" s="1" t="str">
         <f t="shared" ref="T32" si="20">_xlfn.CONCAT("['", C24, "' , '", C25, "' , '", C28, "' , '", C29, "']")</f>
-        <v>['\\lambda_{3}' , '\\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
+        <v>['\lambda_{3}' , '\mu_{3}' , 'c_{3}' , 'K_{3}']</v>
       </c>
       <c r="U32" s="1" t="str">
         <f t="shared" si="19"/>
@@ -18027,7 +16895,7 @@
       </c>
       <c r="T33" s="1" t="str">
         <f t="shared" ref="T33" si="21">_xlfn.CONCAT("['", C27, "' , '", C31, "']")</f>
-        <v>['\\chi_{3}' , 'L_{3}']</v>
+        <v>['\chi_{3}' , 'L_{3}']</v>
       </c>
       <c r="U33" s="1" t="str">
         <f t="shared" si="19"/>
@@ -18109,7 +16977,7 @@
       </c>
       <c r="T34" s="1" t="str">
         <f t="shared" ref="T34" si="22">_xlfn.CONCAT("['", C27, "' , '", C32, "']")</f>
-        <v>['\\chi_{3}' , 'Lq_{3}']</v>
+        <v>['\chi_{3}' , 'Lq_{3}']</v>
       </c>
       <c r="U34" s="1" t="str">
         <f t="shared" si="19"/>
@@ -18125,8 +16993,8 @@
         <v>4</v>
       </c>
       <c r="C35" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{4}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{4}</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -18154,7 +17022,7 @@
       </c>
       <c r="J35" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K35" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18209,8 +17077,8 @@
         <v>4</v>
       </c>
       <c r="C36" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{4}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{4}</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -18238,7 +17106,7 @@
       </c>
       <c r="J36" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K36" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18322,7 +17190,7 @@
       </c>
       <c r="J37" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18375,8 +17243,8 @@
         <v>4</v>
       </c>
       <c r="C38" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{4}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{4}</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -18404,7 +17272,7 @@
       </c>
       <c r="J38" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18443,7 +17311,7 @@
       </c>
       <c r="T38" s="1" t="str">
         <f t="shared" ref="T38" si="23">_xlfn.CONCAT("['", C36, "' , '", C37, "']")</f>
-        <v>['\\mu_{4}' , 'err_{4}']</v>
+        <v>['\mu_{4}' , 'err_{4}']</v>
       </c>
       <c r="U38" s="1" t="str">
         <f t="shared" ref="U38" si="24">_xlfn.CONCAT("{", "}")</f>
@@ -18488,7 +17356,7 @@
       </c>
       <c r="J39" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K39" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18572,7 +17440,7 @@
       </c>
       <c r="J40" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K40" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18627,8 +17495,8 @@
         <v>4</v>
       </c>
       <c r="C41" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{4}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{4}</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -18656,7 +17524,7 @@
       </c>
       <c r="J41" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K41" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18738,7 +17606,7 @@
       </c>
       <c r="J42" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K42" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18777,7 +17645,7 @@
       </c>
       <c r="T42" s="1" t="str">
         <f t="shared" ref="T42" si="26">_xlfn.CONCAT("['", C35, "' , '", C36, "' , '", C39, "' , '", C40, "']")</f>
-        <v>['\\lambda_{4}' , '\\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
+        <v>['\lambda_{4}' , '\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
       </c>
       <c r="U42" s="1" t="str">
         <f t="shared" ref="U42:U45" si="27">_xlfn.CONCAT("{", "}")</f>
@@ -18822,7 +17690,7 @@
       </c>
       <c r="J43" s="1" t="str">
         <f t="shared" si="17"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K43" s="1" t="str">
         <f t="shared" si="17"/>
@@ -18861,7 +17729,7 @@
       </c>
       <c r="T43" s="1" t="str">
         <f t="shared" ref="T43" si="28">_xlfn.CONCAT("['", C35, "' , '", C36, "' , '", C39, "' , '", C40, "']")</f>
-        <v>['\\lambda_{4}' , '\\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
+        <v>['\lambda_{4}' , '\mu_{4}' , 'c_{4}' , 'K_{4}']</v>
       </c>
       <c r="U43" s="1" t="str">
         <f t="shared" si="27"/>
@@ -18943,7 +17811,7 @@
       </c>
       <c r="T44" s="1" t="str">
         <f t="shared" ref="T44" si="29">_xlfn.CONCAT("['", C38, "' , '", C42, "']")</f>
-        <v>['\\chi_{4}' , 'L_{4}']</v>
+        <v>['\chi_{4}' , 'L_{4}']</v>
       </c>
       <c r="U44" s="1" t="str">
         <f t="shared" si="27"/>
@@ -19025,7 +17893,7 @@
       </c>
       <c r="T45" s="1" t="str">
         <f t="shared" ref="T45" si="30">_xlfn.CONCAT("['", C38, "' , '", C43, "']")</f>
-        <v>['\\chi_{4}' , 'Lq_{4}']</v>
+        <v>['\chi_{4}' , 'Lq_{4}']</v>
       </c>
       <c r="U45" s="1" t="str">
         <f t="shared" si="27"/>
@@ -19041,8 +17909,8 @@
         <v>5</v>
       </c>
       <c r="C46" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{5}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{5}</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -19070,7 +17938,7 @@
       </c>
       <c r="J46" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K46" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19124,8 +17992,8 @@
         <v>5</v>
       </c>
       <c r="C47" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{5}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{5}</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -19153,7 +18021,7 @@
       </c>
       <c r="J47" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K47" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19237,7 +18105,7 @@
       </c>
       <c r="J48" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K48" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19291,8 +18159,8 @@
         <v>5</v>
       </c>
       <c r="C49" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{5}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{5}</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -19320,7 +18188,7 @@
       </c>
       <c r="J49" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K49" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19359,7 +18227,7 @@
       </c>
       <c r="T49" s="1" t="str">
         <f t="shared" ref="T49" si="32">_xlfn.CONCAT("['", C47, "' , '", C48, "']")</f>
-        <v>['\\mu_{5}' , 'err_{5}']</v>
+        <v>['\mu_{5}' , 'err_{5}']</v>
       </c>
       <c r="U49" s="1" t="str">
         <f t="shared" ref="U49" si="33">_xlfn.CONCAT("{", "}")</f>
@@ -19404,7 +18272,7 @@
       </c>
       <c r="J50" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K50" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19488,7 +18356,7 @@
       </c>
       <c r="J51" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K51" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19543,8 +18411,8 @@
         <v>5</v>
       </c>
       <c r="C52" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{5}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{5}</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -19571,7 +18439,7 @@
       </c>
       <c r="J52" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K52" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19653,7 +18521,7 @@
       </c>
       <c r="J53" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K53" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19692,7 +18560,7 @@
       </c>
       <c r="T53" s="1" t="str">
         <f t="shared" ref="T53" si="35">_xlfn.CONCAT("['", C46, "' , '", C47, "' , '", C50, "' , '", C51, "']")</f>
-        <v>['\\lambda_{5}' , '\\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
+        <v>['\lambda_{5}' , '\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
       </c>
       <c r="U53" s="1" t="str">
         <f t="shared" ref="U53:U56" si="36">_xlfn.CONCAT("{", "}")</f>
@@ -19737,7 +18605,7 @@
       </c>
       <c r="J54" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K54" s="1" t="str">
         <f t="shared" si="31"/>
@@ -19776,7 +18644,7 @@
       </c>
       <c r="T54" s="1" t="str">
         <f t="shared" ref="T54" si="37">_xlfn.CONCAT("['", C46, "' , '", C47, "' , '", C50, "' , '", C51, "']")</f>
-        <v>['\\lambda_{5}' , '\\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
+        <v>['\lambda_{5}' , '\mu_{5}' , 'c_{5}' , 'K_{5}']</v>
       </c>
       <c r="U54" s="1" t="str">
         <f t="shared" si="36"/>
@@ -19858,7 +18726,7 @@
       </c>
       <c r="T55" s="1" t="str">
         <f t="shared" ref="T55" si="38">_xlfn.CONCAT("['", C49, "' , '", C53, "']")</f>
-        <v>['\\chi_{5}' , 'L_{5}']</v>
+        <v>['\chi_{5}' , 'L_{5}']</v>
       </c>
       <c r="U55" s="1" t="str">
         <f t="shared" si="36"/>
@@ -19940,7 +18808,7 @@
       </c>
       <c r="T56" s="1" t="str">
         <f t="shared" ref="T56" si="39">_xlfn.CONCAT("['", C49, "' , '", C54, "']")</f>
-        <v>['\\chi_{5}' , 'Lq_{5}']</v>
+        <v>['\chi_{5}' , 'Lq_{5}']</v>
       </c>
       <c r="U56" s="1" t="str">
         <f t="shared" si="36"/>
@@ -19956,8 +18824,8 @@
         <v>6</v>
       </c>
       <c r="C57" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{6}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{6}</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -19985,7 +18853,7 @@
       </c>
       <c r="J57" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="31"/>
@@ -20039,8 +18907,8 @@
         <v>6</v>
       </c>
       <c r="C58" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{6}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{6}</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -20068,7 +18936,7 @@
       </c>
       <c r="J58" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="31"/>
@@ -20152,7 +19020,7 @@
       </c>
       <c r="J59" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="31"/>
@@ -20206,8 +19074,8 @@
         <v>6</v>
       </c>
       <c r="C60" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{6}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{6}</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -20235,7 +19103,7 @@
       </c>
       <c r="J60" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="31"/>
@@ -20274,7 +19142,7 @@
       </c>
       <c r="T60" s="1" t="str">
         <f t="shared" ref="T60" si="40">_xlfn.CONCAT("['", C58, "' , '", C59, "']")</f>
-        <v>['\\mu_{6}' , 'err_{6}']</v>
+        <v>['\mu_{6}' , 'err_{6}']</v>
       </c>
       <c r="U60" s="1" t="str">
         <f t="shared" ref="U60" si="41">_xlfn.CONCAT("{", "}")</f>
@@ -20319,7 +19187,7 @@
       </c>
       <c r="J61" s="1" t="str">
         <f t="shared" si="31"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="31"/>
@@ -20403,7 +19271,7 @@
       </c>
       <c r="J62" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K62" s="1" t="str">
         <f t="shared" si="42"/>
@@ -20458,8 +19326,8 @@
         <v>6</v>
       </c>
       <c r="C63" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{6}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{6}</v>
       </c>
       <c r="D63" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -20487,7 +19355,7 @@
       </c>
       <c r="J63" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K63" s="1" t="str">
         <f t="shared" si="42"/>
@@ -20569,7 +19437,7 @@
       </c>
       <c r="J64" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K64" s="1" t="str">
         <f t="shared" si="42"/>
@@ -20608,7 +19476,7 @@
       </c>
       <c r="T64" s="1" t="str">
         <f t="shared" ref="T64" si="44">_xlfn.CONCAT("['", C57, "' , '", C58, "' , '", C61, "' , '", C62, "']")</f>
-        <v>['\\lambda_{6}' , '\\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
+        <v>['\lambda_{6}' , '\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
       </c>
       <c r="U64" s="1" t="str">
         <f t="shared" ref="U64:U67" si="45">_xlfn.CONCAT("{", "}")</f>
@@ -20653,7 +19521,7 @@
       </c>
       <c r="J65" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K65" s="1" t="str">
         <f t="shared" si="42"/>
@@ -20692,7 +19560,7 @@
       </c>
       <c r="T65" s="1" t="str">
         <f t="shared" ref="T65" si="46">_xlfn.CONCAT("['", C57, "' , '", C58, "' , '", C61, "' , '", C62, "']")</f>
-        <v>['\\lambda_{6}' , '\\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
+        <v>['\lambda_{6}' , '\mu_{6}' , 'c_{6}' , 'K_{6}']</v>
       </c>
       <c r="U65" s="1" t="str">
         <f t="shared" si="45"/>
@@ -20774,7 +19642,7 @@
       </c>
       <c r="T66" s="1" t="str">
         <f t="shared" ref="T66" si="47">_xlfn.CONCAT("['", C60, "' , '", C64, "']")</f>
-        <v>['\\chi_{6}' , 'L_{6}']</v>
+        <v>['\chi_{6}' , 'L_{6}']</v>
       </c>
       <c r="U66" s="1" t="str">
         <f t="shared" si="45"/>
@@ -20856,7 +19724,7 @@
       </c>
       <c r="T67" s="1" t="str">
         <f t="shared" ref="T67" si="48">_xlfn.CONCAT("['", C60, "' , '", C65, "']")</f>
-        <v>['\\chi_{6}' , 'Lq_{6}']</v>
+        <v>['\chi_{6}' , 'Lq_{6}']</v>
       </c>
       <c r="U67" s="1" t="str">
         <f t="shared" si="45"/>
@@ -20872,8 +19740,8 @@
         <v>7</v>
       </c>
       <c r="C68" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{7}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{7}</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -20901,7 +19769,7 @@
       </c>
       <c r="J68" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K68" s="1" t="str">
         <f t="shared" si="42"/>
@@ -20955,8 +19823,8 @@
         <v>7</v>
       </c>
       <c r="C69" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{7}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{7}</v>
       </c>
       <c r="D69" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -20984,7 +19852,7 @@
       </c>
       <c r="J69" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K69" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21068,7 +19936,7 @@
       </c>
       <c r="J70" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K70" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21122,8 +19990,8 @@
         <v>7</v>
       </c>
       <c r="C71" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{7}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{7}</v>
       </c>
       <c r="D71" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -21151,7 +20019,7 @@
       </c>
       <c r="J71" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K71" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21190,7 +20058,7 @@
       </c>
       <c r="T71" s="1" t="str">
         <f t="shared" ref="T71" si="49">_xlfn.CONCAT("['", C69, "' , '", C70, "']")</f>
-        <v>['\\mu_{7}' , 'err_{7}']</v>
+        <v>['\mu_{7}' , 'err_{7}']</v>
       </c>
       <c r="U71" s="1" t="str">
         <f t="shared" ref="U71" si="50">_xlfn.CONCAT("{", "}")</f>
@@ -21235,7 +20103,7 @@
       </c>
       <c r="J72" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K72" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21319,7 +20187,7 @@
       </c>
       <c r="J73" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K73" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21374,8 +20242,8 @@
         <v>7</v>
       </c>
       <c r="C74" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{7}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{7}</v>
       </c>
       <c r="D74" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -21403,7 +20271,7 @@
       </c>
       <c r="J74" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K74" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21485,7 +20353,7 @@
       </c>
       <c r="J75" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K75" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21524,7 +20392,7 @@
       </c>
       <c r="T75" s="1" t="str">
         <f t="shared" ref="T75" si="52">_xlfn.CONCAT("['", C68, "' , '", C69, "' , '", C72, "' , '", C73, "']")</f>
-        <v>['\\lambda_{7}' , '\\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
+        <v>['\lambda_{7}' , '\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
       </c>
       <c r="U75" s="1" t="str">
         <f t="shared" ref="U75:U78" si="53">_xlfn.CONCAT("{", "}")</f>
@@ -21569,7 +20437,7 @@
       </c>
       <c r="J76" s="1" t="str">
         <f t="shared" si="42"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K76" s="1" t="str">
         <f t="shared" si="42"/>
@@ -21608,7 +20476,7 @@
       </c>
       <c r="T76" s="1" t="str">
         <f t="shared" ref="T76" si="54">_xlfn.CONCAT("['", C68, "' , '", C69, "' , '", C72, "' , '", C73, "']")</f>
-        <v>['\\lambda_{7}' , '\\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
+        <v>['\lambda_{7}' , '\mu_{7}' , 'c_{7}' , 'K_{7}']</v>
       </c>
       <c r="U76" s="1" t="str">
         <f t="shared" si="53"/>
@@ -21690,7 +20558,7 @@
       </c>
       <c r="T77" s="1" t="str">
         <f t="shared" ref="T77" si="55">_xlfn.CONCAT("['", C71, "' , '", C75, "']")</f>
-        <v>['\\chi_{7}' , 'L_{7}']</v>
+        <v>['\chi_{7}' , 'L_{7}']</v>
       </c>
       <c r="U77" s="1" t="str">
         <f t="shared" si="53"/>
@@ -21772,7 +20640,7 @@
       </c>
       <c r="T78" s="1" t="str">
         <f t="shared" ref="T78" si="60">_xlfn.CONCAT("['", C71, "' , '", C76, "']")</f>
-        <v>['\\chi_{7}' , 'Lq_{7}']</v>
+        <v>['\chi_{7}' , 'Lq_{7}']</v>
       </c>
       <c r="U78" s="1" t="str">
         <f t="shared" si="53"/>
@@ -21788,8 +20656,8 @@
         <v>8</v>
       </c>
       <c r="C79" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{8}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{8}</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -21817,7 +20685,7 @@
       </c>
       <c r="J79" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K79" s="1" t="str">
         <f t="shared" si="58"/>
@@ -21872,8 +20740,8 @@
         <v>8</v>
       </c>
       <c r="C80" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{8}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{8}</v>
       </c>
       <c r="D80" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -21901,7 +20769,7 @@
       </c>
       <c r="J80" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K80" s="1" t="str">
         <f t="shared" si="58"/>
@@ -21985,7 +20853,7 @@
       </c>
       <c r="J81" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K81" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22038,8 +20906,8 @@
         <v>8</v>
       </c>
       <c r="C82" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{8}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{8}</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -22067,7 +20935,7 @@
       </c>
       <c r="J82" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K82" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22106,7 +20974,7 @@
       </c>
       <c r="T82" s="1" t="str">
         <f t="shared" ref="T82" si="61">_xlfn.CONCAT("['", C80, "' , '", C81, "']")</f>
-        <v>['\\mu_{8}' , 'err_{8}']</v>
+        <v>['\mu_{8}' , 'err_{8}']</v>
       </c>
       <c r="U82" s="1" t="str">
         <f t="shared" ref="U82" si="62">_xlfn.CONCAT("{", "}")</f>
@@ -22151,7 +21019,7 @@
       </c>
       <c r="J83" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K83" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22235,7 +21103,7 @@
       </c>
       <c r="J84" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K84" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22290,8 +21158,8 @@
         <v>8</v>
       </c>
       <c r="C85" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{8}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{8}</v>
       </c>
       <c r="D85" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -22319,7 +21187,7 @@
       </c>
       <c r="J85" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K85" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22401,7 +21269,7 @@
       </c>
       <c r="J86" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K86" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22440,7 +21308,7 @@
       </c>
       <c r="T86" s="1" t="str">
         <f t="shared" ref="T86" si="64">_xlfn.CONCAT("['", C79, "' , '", C80, "' , '", C83, "' , '", C84, "']")</f>
-        <v>['\\lambda_{8}' , '\\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
+        <v>['\lambda_{8}' , '\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
       </c>
       <c r="U86" s="1" t="str">
         <f t="shared" ref="U86:U89" si="65">_xlfn.CONCAT("{", "}")</f>
@@ -22485,7 +21353,7 @@
       </c>
       <c r="J87" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K87" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22524,7 +21392,7 @@
       </c>
       <c r="T87" s="1" t="str">
         <f t="shared" ref="T87" si="66">_xlfn.CONCAT("['", C79, "' , '", C80, "' , '", C83, "' , '", C84, "']")</f>
-        <v>['\\lambda_{8}' , '\\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
+        <v>['\lambda_{8}' , '\mu_{8}' , 'c_{8}' , 'K_{8}']</v>
       </c>
       <c r="U87" s="1" t="str">
         <f t="shared" si="65"/>
@@ -22606,7 +21474,7 @@
       </c>
       <c r="T88" s="1" t="str">
         <f t="shared" ref="T88" si="67">_xlfn.CONCAT("['", C82, "' , '", C86, "']")</f>
-        <v>['\\chi_{8}' , 'L_{8}']</v>
+        <v>['\chi_{8}' , 'L_{8}']</v>
       </c>
       <c r="U88" s="1" t="str">
         <f t="shared" si="65"/>
@@ -22688,7 +21556,7 @@
       </c>
       <c r="T89" s="1" t="str">
         <f t="shared" ref="T89" si="68">_xlfn.CONCAT("['", C82, "' , '", C87, "']")</f>
-        <v>['\\chi_{8}' , 'Lq_{8}']</v>
+        <v>['\chi_{8}' , 'Lq_{8}']</v>
       </c>
       <c r="U89" s="1" t="str">
         <f t="shared" si="65"/>
@@ -22704,8 +21572,8 @@
         <v>9</v>
       </c>
       <c r="C90" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{9}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{9}</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -22733,7 +21601,7 @@
       </c>
       <c r="J90" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K90" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22788,8 +21656,8 @@
         <v>9</v>
       </c>
       <c r="C91" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{9}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{9}</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -22817,7 +21685,7 @@
       </c>
       <c r="J91" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K91" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22901,7 +21769,7 @@
       </c>
       <c r="J92" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K92" s="1" t="str">
         <f t="shared" si="58"/>
@@ -22954,8 +21822,8 @@
         <v>9</v>
       </c>
       <c r="C93" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{9}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{9}</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -22983,7 +21851,7 @@
       </c>
       <c r="J93" s="1" t="str">
         <f t="shared" si="58"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K93" s="1" t="str">
         <f t="shared" si="58"/>
@@ -23022,7 +21890,7 @@
       </c>
       <c r="T93" s="1" t="str">
         <f t="shared" ref="T93" si="69">_xlfn.CONCAT("['", C91, "' , '", C92, "']")</f>
-        <v>['\\mu_{9}' , 'err_{9}']</v>
+        <v>['\mu_{9}' , 'err_{9}']</v>
       </c>
       <c r="U93" s="1" t="str">
         <f t="shared" ref="U93" si="70">_xlfn.CONCAT("{", "}")</f>
@@ -23067,7 +21935,7 @@
       </c>
       <c r="J94" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K94" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23151,7 +22019,7 @@
       </c>
       <c r="J95" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K95" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23206,8 +22074,8 @@
         <v>9</v>
       </c>
       <c r="C96" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{9}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{9}</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -23235,7 +22103,7 @@
       </c>
       <c r="J96" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K96" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23317,7 +22185,7 @@
       </c>
       <c r="J97" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K97" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23356,7 +22224,7 @@
       </c>
       <c r="T97" s="1" t="str">
         <f t="shared" ref="T97" si="73">_xlfn.CONCAT("['", C90, "' , '", C91, "' , '", C94, "' , '", C95, "']")</f>
-        <v>['\\lambda_{9}' , '\\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
+        <v>['\lambda_{9}' , '\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
       </c>
       <c r="U97" s="1" t="str">
         <f t="shared" ref="U97:U100" si="74">_xlfn.CONCAT("{", "}")</f>
@@ -23401,7 +22269,7 @@
       </c>
       <c r="J98" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K98" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23440,7 +22308,7 @@
       </c>
       <c r="T98" s="1" t="str">
         <f t="shared" ref="T98" si="76">_xlfn.CONCAT("['", C90, "' , '", C91, "' , '", C94, "' , '", C95, "']")</f>
-        <v>['\\lambda_{9}' , '\\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
+        <v>['\lambda_{9}' , '\mu_{9}' , 'c_{9}' , 'K_{9}']</v>
       </c>
       <c r="U98" s="1" t="str">
         <f t="shared" si="74"/>
@@ -23522,7 +22390,7 @@
       </c>
       <c r="T99" s="1" t="str">
         <f t="shared" ref="T99" si="77">_xlfn.CONCAT("['", C93, "' , '", C97, "']")</f>
-        <v>['\\chi_{9}' , 'L_{9}']</v>
+        <v>['\chi_{9}' , 'L_{9}']</v>
       </c>
       <c r="U99" s="1" t="str">
         <f t="shared" si="74"/>
@@ -23604,7 +22472,7 @@
       </c>
       <c r="T100" s="1" t="str">
         <f t="shared" ref="T100" si="78">_xlfn.CONCAT("['", C93, "' , '", C98, "']")</f>
-        <v>['\\chi_{9}' , 'Lq_{9}']</v>
+        <v>['\chi_{9}' , 'Lq_{9}']</v>
       </c>
       <c r="U100" s="1" t="str">
         <f t="shared" si="74"/>
@@ -23620,8 +22488,8 @@
         <v>10</v>
       </c>
       <c r="C101" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{10}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{10}</v>
       </c>
       <c r="D101" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -23649,7 +22517,7 @@
       </c>
       <c r="J101" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K101" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23704,8 +22572,8 @@
         <v>10</v>
       </c>
       <c r="C102" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{10}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{10}</v>
       </c>
       <c r="D102" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -23733,7 +22601,7 @@
       </c>
       <c r="J102" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K102" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23817,7 +22685,7 @@
       </c>
       <c r="J103" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K103" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23870,8 +22738,8 @@
         <v>10</v>
       </c>
       <c r="C104" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{10}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{10}</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -23899,7 +22767,7 @@
       </c>
       <c r="J104" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K104" s="1" t="str">
         <f t="shared" si="71"/>
@@ -23938,7 +22806,7 @@
       </c>
       <c r="T104" s="1" t="str">
         <f t="shared" ref="T104" si="79">_xlfn.CONCAT("['", C102, "' , '", C103, "']")</f>
-        <v>['\\mu_{10}' , 'err_{10}']</v>
+        <v>['\mu_{10}' , 'err_{10}']</v>
       </c>
       <c r="U104" s="1" t="str">
         <f t="shared" ref="U104" si="80">_xlfn.CONCAT("{", "}")</f>
@@ -23983,7 +22851,7 @@
       </c>
       <c r="J105" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K105" s="1" t="str">
         <f t="shared" si="71"/>
@@ -24067,7 +22935,7 @@
       </c>
       <c r="J106" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K106" s="1" t="str">
         <f t="shared" si="71"/>
@@ -24122,8 +22990,8 @@
         <v>10</v>
       </c>
       <c r="C107" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{10}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{10}</v>
       </c>
       <c r="D107" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -24151,7 +23019,7 @@
       </c>
       <c r="J107" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K107" s="1" t="str">
         <f t="shared" si="71"/>
@@ -24233,7 +23101,7 @@
       </c>
       <c r="J108" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K108" s="1" t="str">
         <f t="shared" si="71"/>
@@ -24272,7 +23140,7 @@
       </c>
       <c r="T108" s="1" t="str">
         <f t="shared" ref="T108" si="82">_xlfn.CONCAT("['", C101, "' , '", C102, "' , '", C105, "' , '", C106, "']")</f>
-        <v>['\\lambda_{10}' , '\\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
+        <v>['\lambda_{10}' , '\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
       </c>
       <c r="U108" s="1" t="str">
         <f t="shared" ref="U108:U111" si="83">_xlfn.CONCAT("{", "}")</f>
@@ -24317,7 +23185,7 @@
       </c>
       <c r="J109" s="1" t="str">
         <f t="shared" si="71"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K109" s="1" t="str">
         <f t="shared" si="71"/>
@@ -24356,7 +23224,7 @@
       </c>
       <c r="T109" s="1" t="str">
         <f t="shared" ref="T109" si="84">_xlfn.CONCAT("['", C101, "' , '", C102, "' , '", C105, "' , '", C106, "']")</f>
-        <v>['\\lambda_{10}' , '\\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
+        <v>['\lambda_{10}' , '\mu_{10}' , 'c_{10}' , 'K_{10}']</v>
       </c>
       <c r="U109" s="1" t="str">
         <f t="shared" si="83"/>
@@ -24438,7 +23306,7 @@
       </c>
       <c r="T110" s="1" t="str">
         <f t="shared" ref="T110" si="86">_xlfn.CONCAT("['", C104, "' , '", C108, "']")</f>
-        <v>['\\chi_{10}' , 'L_{10}']</v>
+        <v>['\chi_{10}' , 'L_{10}']</v>
       </c>
       <c r="U110" s="1" t="str">
         <f t="shared" si="83"/>
@@ -24520,7 +23388,7 @@
       </c>
       <c r="T111" s="1" t="str">
         <f t="shared" ref="T111" si="87">_xlfn.CONCAT("['", C104, "' , '", C109, "']")</f>
-        <v>['\\chi_{10}' , 'Lq_{10}']</v>
+        <v>['\chi_{10}' , 'Lq_{10}']</v>
       </c>
       <c r="U111" s="1" t="str">
         <f t="shared" si="83"/>
@@ -24536,8 +23404,8 @@
         <v>11</v>
       </c>
       <c r="C112" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{11}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{11}</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -24565,7 +23433,7 @@
       </c>
       <c r="J112" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K112" s="1" t="str">
         <f t="shared" si="85"/>
@@ -24620,8 +23488,8 @@
         <v>11</v>
       </c>
       <c r="C113" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{11}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{11}</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -24649,7 +23517,7 @@
       </c>
       <c r="J113" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K113" s="1" t="str">
         <f t="shared" si="85"/>
@@ -24732,8 +23600,8 @@
         <v>CTRL</v>
       </c>
       <c r="J114" s="1" t="str">
-        <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <f>J103</f>
+        <v>E*T^-1</v>
       </c>
       <c r="K114" s="1" t="str">
         <f t="shared" si="85"/>
@@ -24786,8 +23654,8 @@
         <v>11</v>
       </c>
       <c r="C115" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{11}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{11}</v>
       </c>
       <c r="D115" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -24815,7 +23683,7 @@
       </c>
       <c r="J115" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K115" s="1" t="str">
         <f t="shared" si="85"/>
@@ -24854,7 +23722,7 @@
       </c>
       <c r="T115" s="1" t="str">
         <f t="shared" ref="T115" si="88">_xlfn.CONCAT("['", C113, "' , '", C114, "']")</f>
-        <v>['\\mu_{11}' , 'err_{11}']</v>
+        <v>['\mu_{11}' , 'err_{11}']</v>
       </c>
       <c r="U115" s="1" t="str">
         <f t="shared" ref="U115" si="89">_xlfn.CONCAT("{", "}")</f>
@@ -24899,7 +23767,7 @@
       </c>
       <c r="J116" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K116" s="1" t="str">
         <f t="shared" si="85"/>
@@ -24983,7 +23851,7 @@
       </c>
       <c r="J117" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K117" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25038,8 +23906,8 @@
         <v>11</v>
       </c>
       <c r="C118" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{11}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{11}</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -25067,7 +23935,7 @@
       </c>
       <c r="J118" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K118" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25149,7 +24017,7 @@
       </c>
       <c r="J119" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K119" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25188,7 +24056,7 @@
       </c>
       <c r="T119" s="1" t="str">
         <f t="shared" ref="T119" si="92">_xlfn.CONCAT("['", C112, "' , '", C113, "' , '", C116, "' , '", C117, "']")</f>
-        <v>['\\lambda_{11}' , '\\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
+        <v>['\lambda_{11}' , '\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
       </c>
       <c r="U119" s="1" t="str">
         <f t="shared" ref="U119:U122" si="93">_xlfn.CONCAT("{", "}")</f>
@@ -25233,7 +24101,7 @@
       </c>
       <c r="J120" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K120" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25272,7 +24140,7 @@
       </c>
       <c r="T120" s="1" t="str">
         <f t="shared" ref="T120" si="94">_xlfn.CONCAT("['", C112, "' , '", C113, "' , '", C116, "' , '", C117, "']")</f>
-        <v>['\\lambda_{11}' , '\\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
+        <v>['\lambda_{11}' , '\mu_{11}' , 'c_{11}' , 'K_{11}']</v>
       </c>
       <c r="U120" s="1" t="str">
         <f t="shared" si="93"/>
@@ -25354,7 +24222,7 @@
       </c>
       <c r="T121" s="1" t="str">
         <f t="shared" ref="T121" si="95">_xlfn.CONCAT("['", C115, "' , '", C119, "']")</f>
-        <v>['\\chi_{11}' , 'L_{11}']</v>
+        <v>['\chi_{11}' , 'L_{11}']</v>
       </c>
       <c r="U121" s="1" t="str">
         <f t="shared" si="93"/>
@@ -25436,7 +24304,7 @@
       </c>
       <c r="T122" s="1" t="str">
         <f t="shared" ref="T122" si="96">_xlfn.CONCAT("['", C115, "' , '", C120, "']")</f>
-        <v>['\\chi_{11}' , 'Lq_{11}']</v>
+        <v>['\chi_{11}' , 'Lq_{11}']</v>
       </c>
       <c r="U122" s="1" t="str">
         <f t="shared" si="93"/>
@@ -25452,8 +24320,8 @@
         <v>12</v>
       </c>
       <c r="C123" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{12}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{12}</v>
       </c>
       <c r="D123" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -25481,7 +24349,7 @@
       </c>
       <c r="J123" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K123" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25536,8 +24404,8 @@
         <v>12</v>
       </c>
       <c r="C124" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{12}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{12}</v>
       </c>
       <c r="D124" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -25565,7 +24433,7 @@
       </c>
       <c r="J124" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K124" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25649,7 +24517,7 @@
       </c>
       <c r="J125" s="1" t="str">
         <f t="shared" si="85"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K125" s="1" t="str">
         <f t="shared" si="85"/>
@@ -25702,8 +24570,8 @@
         <v>12</v>
       </c>
       <c r="C126" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{12}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{12}</v>
       </c>
       <c r="D126" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -25731,7 +24599,7 @@
       </c>
       <c r="J126" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K126" s="1" t="str">
         <f t="shared" si="97"/>
@@ -25770,7 +24638,7 @@
       </c>
       <c r="T126" s="1" t="str">
         <f t="shared" ref="T126" si="98">_xlfn.CONCAT("['", C124, "' , '", C125, "']")</f>
-        <v>['\\mu_{12}' , 'err_{12}']</v>
+        <v>['\mu_{12}' , 'err_{12}']</v>
       </c>
       <c r="U126" s="1" t="str">
         <f t="shared" ref="U126" si="99">_xlfn.CONCAT("{", "}")</f>
@@ -25815,7 +24683,7 @@
       </c>
       <c r="J127" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K127" s="1" t="str">
         <f t="shared" si="97"/>
@@ -25899,7 +24767,7 @@
       </c>
       <c r="J128" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K128" s="1" t="str">
         <f t="shared" si="97"/>
@@ -25954,8 +24822,8 @@
         <v>12</v>
       </c>
       <c r="C129" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{12}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{12}</v>
       </c>
       <c r="D129" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -25983,7 +24851,7 @@
       </c>
       <c r="J129" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K129" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26065,7 +24933,7 @@
       </c>
       <c r="J130" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K130" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26104,7 +24972,7 @@
       </c>
       <c r="T130" s="1" t="str">
         <f t="shared" ref="T130" si="101">_xlfn.CONCAT("['", C123, "' , '", C124, "' , '", C127, "' , '", C128, "']")</f>
-        <v>['\\lambda_{12}' , '\\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
+        <v>['\lambda_{12}' , '\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
       </c>
       <c r="U130" s="1" t="str">
         <f t="shared" ref="U130:U133" si="102">_xlfn.CONCAT("{", "}")</f>
@@ -26149,7 +25017,7 @@
       </c>
       <c r="J131" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K131" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26188,7 +25056,7 @@
       </c>
       <c r="T131" s="1" t="str">
         <f t="shared" ref="T131" si="103">_xlfn.CONCAT("['", C123, "' , '", C124, "' , '", C127, "' , '", C128, "']")</f>
-        <v>['\\lambda_{12}' , '\\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
+        <v>['\lambda_{12}' , '\mu_{12}' , 'c_{12}' , 'K_{12}']</v>
       </c>
       <c r="U131" s="1" t="str">
         <f t="shared" si="102"/>
@@ -26270,7 +25138,7 @@
       </c>
       <c r="T132" s="1" t="str">
         <f t="shared" ref="T132" si="104">_xlfn.CONCAT("['", C126, "' , '", C130, "']")</f>
-        <v>['\\chi_{12}' , 'L_{12}']</v>
+        <v>['\chi_{12}' , 'L_{12}']</v>
       </c>
       <c r="U132" s="1" t="str">
         <f t="shared" si="102"/>
@@ -26352,7 +25220,7 @@
       </c>
       <c r="T133" s="1" t="str">
         <f t="shared" ref="T133" si="105">_xlfn.CONCAT("['", C126, "' , '", C131, "']")</f>
-        <v>['\\chi_{12}' , 'Lq_{12}']</v>
+        <v>['\chi_{12}' , 'Lq_{12}']</v>
       </c>
       <c r="U133" s="1" t="str">
         <f t="shared" si="102"/>
@@ -26368,8 +25236,8 @@
         <v>13</v>
       </c>
       <c r="C134" s="1" t="str">
-        <f>_xlfn.CONCAT("\\lambda_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\lambda_{13}</v>
+        <f>_xlfn.CONCAT("\lambda_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\lambda_{13}</v>
       </c>
       <c r="D134" s="1" t="str">
         <f>_xlfn.CONCAT("lambda_tas_", Table16[[#This Row],[dm]])</f>
@@ -26397,7 +25265,7 @@
       </c>
       <c r="J134" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K134" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26452,8 +25320,8 @@
         <v>13</v>
       </c>
       <c r="C135" s="1" t="str">
-        <f>_xlfn.CONCAT("\\mu_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\mu_{13}</v>
+        <f>_xlfn.CONCAT("\mu_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\mu_{13}</v>
       </c>
       <c r="D135" s="1" t="str">
         <f>_xlfn.CONCAT("mu_tas_", Table16[[#This Row],[dm]])</f>
@@ -26481,7 +25349,7 @@
       </c>
       <c r="J135" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K135" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26565,7 +25433,7 @@
       </c>
       <c r="J136" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K136" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26618,8 +25486,8 @@
         <v>13</v>
       </c>
       <c r="C137" s="1" t="str">
-        <f>_xlfn.CONCAT("\\chi_{",Table16[[#This Row],[dm]], "}")</f>
-        <v>\\chi_{13}</v>
+        <f>_xlfn.CONCAT("\chi_{",Table16[[#This Row],[dm]], "}")</f>
+        <v>\chi_{13}</v>
       </c>
       <c r="D137" s="1" t="str">
         <f>_xlfn.CONCAT("chi_tas_", Table16[[#This Row],[dm]])</f>
@@ -26647,7 +25515,7 @@
       </c>
       <c r="J137" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I*T^-1</v>
+        <v>E*T^-1</v>
       </c>
       <c r="K137" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26686,7 +25554,7 @@
       </c>
       <c r="T137" s="1" t="str">
         <f t="shared" ref="T137" si="106">_xlfn.CONCAT("['", C135, "' , '", C136, "']")</f>
-        <v>['\\mu_{13}' , 'err_{13}']</v>
+        <v>['\mu_{13}' , 'err_{13}']</v>
       </c>
       <c r="U137" s="1" t="str">
         <f t="shared" ref="U137" si="107">_xlfn.CONCAT("{", "}")</f>
@@ -26731,7 +25599,7 @@
       </c>
       <c r="J138" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K138" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26815,7 +25683,7 @@
       </c>
       <c r="J139" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K139" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26870,8 +25738,8 @@
         <v>13</v>
       </c>
       <c r="C140" s="1" t="str">
-        <f>_xlfn.CONCAT("\\delta_{", Table16[[#This Row],[dm]],"}")</f>
-        <v>\\delta_{13}</v>
+        <f>_xlfn.CONCAT("\delta_{", Table16[[#This Row],[dm]],"}")</f>
+        <v>\delta_{13}</v>
       </c>
       <c r="D140" s="1" t="str">
         <f>_xlfn.CONCAT("delta_tas_", Table16[[#This Row],[dm]])</f>
@@ -26899,7 +25767,7 @@
       </c>
       <c r="J140" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>D*I^-1</v>
+        <v>D*E^-1</v>
       </c>
       <c r="K140" s="1" t="str">
         <f t="shared" si="97"/>
@@ -26981,7 +25849,7 @@
       </c>
       <c r="J141" s="1" t="str">
         <f t="shared" si="97"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K141" s="1" t="str">
         <f t="shared" si="97"/>
@@ -27020,7 +25888,7 @@
       </c>
       <c r="T141" s="1" t="str">
         <f t="shared" ref="T141" si="109">_xlfn.CONCAT("['", C134, "' , '", C135, "' , '", C138, "' , '", C139, "']")</f>
-        <v>['\\lambda_{13}' , '\\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
+        <v>['\lambda_{13}' , '\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
       </c>
       <c r="U141" s="1" t="str">
         <f t="shared" ref="U141:U144" si="110">_xlfn.CONCAT("{", "}")</f>
@@ -27065,7 +25933,7 @@
       </c>
       <c r="J142" s="1" t="str">
         <f t="shared" si="112"/>
-        <v>I</v>
+        <v>E</v>
       </c>
       <c r="K142" s="1" t="str">
         <f t="shared" si="112"/>
@@ -27104,7 +25972,7 @@
       </c>
       <c r="T142" s="1" t="str">
         <f t="shared" ref="T142" si="114">_xlfn.CONCAT("['", C134, "' , '", C135, "' , '", C138, "' , '", C139, "']")</f>
-        <v>['\\lambda_{13}' , '\\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
+        <v>['\lambda_{13}' , '\mu_{13}' , 'c_{13}' , 'K_{13}']</v>
       </c>
       <c r="U142" s="1" t="str">
         <f t="shared" si="110"/>
@@ -27186,7 +26054,7 @@
       </c>
       <c r="T143" s="1" t="str">
         <f t="shared" ref="T143" si="115">_xlfn.CONCAT("['", C137, "' , '", C141, "']")</f>
-        <v>['\\chi_{13}' , 'L_{13}']</v>
+        <v>['\chi_{13}' , 'L_{13}']</v>
       </c>
       <c r="U143" s="1" t="str">
         <f t="shared" si="110"/>
@@ -27268,7 +26136,7 @@
       </c>
       <c r="T144" s="1" t="str">
         <f t="shared" ref="T144" si="116">_xlfn.CONCAT("['", C137, "' , '", C142, "']")</f>
-        <v>['\\chi_{13}' , 'Lq_{13}']</v>
+        <v>['\chi_{13}' , 'Lq_{13}']</v>
       </c>
       <c r="U144" s="1" t="str">
         <f t="shared" si="110"/>
@@ -27285,296 +26153,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91B5509-780C-4AC4-B46F-3966C71D9DD8}">
-  <dimension ref="D3:E31"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="4" max="4" width="14.41015625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.76171875" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="13">
-        <f>50/60</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.5">
-      <c r="D31" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="13">
-        <f>7</f>
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
-  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4178880-1B36-4BB6-91A5-343EFFC60114}">
-  <dimension ref="E2:L40"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="12" max="12" width="30.41015625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="5:12" ht="51.35" x14ac:dyDescent="0.5">
-      <c r="L4" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="L5" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="L6" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="L7" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="L8" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="5:12" ht="38.700000000000003" x14ac:dyDescent="0.5">
-      <c r="L9" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L10" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L11" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L12" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L13" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L14" s="10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L15" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="5:12" x14ac:dyDescent="0.5">
-      <c r="L16" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L17" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L18" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L19" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L20" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L21" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L22" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L23" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L24" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L25" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L26" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L27" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L28" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L29" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L30" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L31" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L32" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L33" s="10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L34" s="10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L35" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L36" s="10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L37" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L38" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L39" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="12:12" x14ac:dyDescent="0.5">
-      <c r="L40" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19AD119-0FB0-4895-85D4-3420B73DEBC1}">
   <dimension ref="A1:U144"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
@@ -27683,7 +26274,7 @@
         <v>lambda_tas_1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " arrival rate")</f>
@@ -27700,7 +26291,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>4</v>
@@ -27760,7 +26351,7 @@
         <v>mu_tas_1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " service rate")</f>
@@ -27777,7 +26368,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>4</v>
@@ -27837,7 +26428,7 @@
         <v>err_tas_1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F4" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " error probability")</f>
@@ -27854,7 +26445,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>31</v>
@@ -27913,7 +26504,7 @@
         <v>chi_tas_1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " departure rate")</f>
@@ -27930,7 +26521,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>4</v>
@@ -27989,7 +26580,7 @@
         <v>c_tas_1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " resourses")</f>
@@ -28006,7 +26597,7 @@
         <v>3</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>7</v>
@@ -28066,7 +26657,7 @@
         <v>K_tas_1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " q-capacity")</f>
@@ -28083,7 +26674,7 @@
         <v>5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>7</v>
@@ -28143,7 +26734,7 @@
         <v>delta_tas_1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F8" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " req data density")</f>
@@ -28160,7 +26751,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -28218,7 +26809,7 @@
         <v>L_tas_1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " mean processing requests")</f>
@@ -28235,7 +26826,7 @@
         <v>5</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>7</v>
@@ -28295,7 +26886,7 @@
         <v>Lq_tas_1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F10" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " mean in memory requests")</f>
@@ -28312,7 +26903,7 @@
         <v>5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>7</v>
@@ -28372,7 +26963,7 @@
         <v>W_tas_1</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " mean time to answer")</f>
@@ -28447,7 +27038,7 @@
         <v>Wq_tas_1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F12" s="1" t="str">
         <f>_xlfn.CONCAT("TAS ", Table167[[#This Row],[dm]], " mean time in buffer")</f>

--- a/assets/cs1/sheet/pydasa_cs1_dim_vars.xlsx
+++ b/assets/cs1/sheet/pydasa_cs1_dim_vars.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bd4428830306c10d/Documents/GitHub/DASA-Design/PyDASA-Case-Studies/assets/cs1/sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="13_ncr:1_{D95395EB-DBE5-4D0C-A905-FDA3E5BFB6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2222844-FF56-4EDA-8ED4-1924873908CD}"/>
+  <xr:revisionPtr revIDLastSave="397" documentId="13_ncr:1_{D95395EB-DBE5-4D0C-A905-FDA3E5BFB6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A09B0224-985C-43D5-9128-20BCACC79703}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4000" yWindow="3967" windowWidth="7540" windowHeight="6000" xr2:uid="{EABAE1E3-9871-4CDD-80AF-2EA34DC987B5}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{EABAE1E3-9871-4CDD-80AF-2EA34DC987B5}"/>
   </bookViews>
   <sheets>
     <sheet name="dflt_relevance_lt@3FDUs" sheetId="1" r:id="rId1"/>
@@ -2654,15 +2654,15 @@
         <v>7</v>
       </c>
       <c r="L7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M7" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N7" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O7" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -2670,15 +2670,15 @@
       </c>
       <c r="P7" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R7" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>33</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="U7" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.5">
@@ -3539,15 +3539,15 @@
         <v>req</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M18" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
-      </c>
-      <c r="N18" s="4">
+        <v>15</v>
+      </c>
+      <c r="N18" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O18" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -3555,15 +3555,15 @@
       </c>
       <c r="P18" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q18" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R18" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S18" s="1" t="str">
         <f t="shared" si="5"/>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="U18" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.5">
@@ -4459,15 +4459,15 @@
         <v>req</v>
       </c>
       <c r="L29" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M29" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N29" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O29" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -4475,15 +4475,15 @@
       </c>
       <c r="P29" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q29" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R29" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S29" s="1" t="str">
         <f t="shared" si="5"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="U29" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.5">
@@ -5379,15 +5379,15 @@
         <v>req</v>
       </c>
       <c r="L40" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M40" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N40" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O40" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -5395,15 +5395,15 @@
       </c>
       <c r="P40" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q40" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R40" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S40" s="1" t="str">
         <f t="shared" si="5"/>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="U40" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.5">
@@ -6219,12 +6219,11 @@
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <f>Table1[[#This Row],[_min]]+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O50" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -6236,11 +6235,11 @@
       </c>
       <c r="Q50" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R50" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S50" s="1" t="str">
         <f t="shared" si="5"/>
@@ -6252,7 +6251,7 @@
       </c>
       <c r="U50" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 2}</v>
+        <v>{'low': 1, 'high': 3}</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.5">
@@ -6300,15 +6299,15 @@
         <v>req</v>
       </c>
       <c r="L51" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M51" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N51" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O51" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -6316,15 +6315,15 @@
       </c>
       <c r="P51" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q51" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R51" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S51" s="1" t="str">
         <f t="shared" si="5"/>
@@ -6336,7 +6335,7 @@
       </c>
       <c r="U51" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.5">
@@ -7221,15 +7220,15 @@
         <v>req</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M62" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N62" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O62" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -7237,15 +7236,15 @@
       </c>
       <c r="P62" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q62" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R62" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S62" s="1" t="str">
         <f t="shared" si="5"/>
@@ -7257,7 +7256,7 @@
       </c>
       <c r="U62" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.5">
@@ -8061,12 +8060,11 @@
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f>Table1[[#This Row],[_min]]+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N72" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O72" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -8078,11 +8076,11 @@
       </c>
       <c r="Q72" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R72" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S72" s="1" t="str">
         <f t="shared" si="5"/>
@@ -8094,7 +8092,7 @@
       </c>
       <c r="U72" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 2}</v>
+        <v>{'low': 1, 'high': 3}</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.5">
@@ -8142,15 +8140,15 @@
         <v>req</v>
       </c>
       <c r="L73" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M73" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N73" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O73" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -8158,15 +8156,15 @@
       </c>
       <c r="P73" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q73" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R73" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S73" s="1" t="str">
         <f t="shared" si="5"/>
@@ -8178,7 +8176,7 @@
       </c>
       <c r="U73" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.5">
@@ -8981,12 +8979,11 @@
         <v>1</v>
       </c>
       <c r="M83" s="1">
-        <f>Table1[[#This Row],[_min]]+1</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N83" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O83" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -8998,11 +8995,11 @@
       </c>
       <c r="Q83" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R83" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S83" s="1" t="str">
         <f t="shared" si="113"/>
@@ -9014,7 +9011,7 @@
       </c>
       <c r="U83" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 2}</v>
+        <v>{'low': 1, 'high': 3}</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.5">
@@ -9062,15 +9059,15 @@
         <v>req</v>
       </c>
       <c r="L84" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M84" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N84" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O84" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -9078,15 +9075,15 @@
       </c>
       <c r="P84" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q84" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R84" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S84" s="1" t="str">
         <f t="shared" si="113"/>
@@ -9098,7 +9095,7 @@
       </c>
       <c r="U84" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.5">
@@ -9982,15 +9979,15 @@
         <v>req</v>
       </c>
       <c r="L95" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M95" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N95" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O95" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -9998,15 +9995,15 @@
       </c>
       <c r="P95" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q95" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R95" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S95" s="1" t="str">
         <f t="shared" si="113"/>
@@ -10018,7 +10015,7 @@
       </c>
       <c r="U95" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.5">
@@ -10902,15 +10899,15 @@
         <v>req</v>
       </c>
       <c r="L106" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M106" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N106" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O106" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -10918,15 +10915,15 @@
       </c>
       <c r="P106" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q106" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R106" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S106" s="1" t="str">
         <f t="shared" si="113"/>
@@ -10938,7 +10935,7 @@
       </c>
       <c r="U106" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.5">
@@ -11822,15 +11819,15 @@
         <v>req</v>
       </c>
       <c r="L117" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M117" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N117" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O117" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -11838,15 +11835,15 @@
       </c>
       <c r="P117" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q117" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R117" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S117" s="1" t="str">
         <f t="shared" si="113"/>
@@ -11858,7 +11855,7 @@
       </c>
       <c r="U117" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.5">
@@ -12742,15 +12739,15 @@
         <v>req</v>
       </c>
       <c r="L128" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M128" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N128" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O128" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -12758,15 +12755,15 @@
       </c>
       <c r="P128" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q128" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R128" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S128" s="1" t="str">
         <f t="shared" si="113"/>
@@ -12778,7 +12775,7 @@
       </c>
       <c r="U128" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.5">
@@ -13662,15 +13659,15 @@
         <v>req</v>
       </c>
       <c r="L139" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M139" s="1">
         <f>Table1[[#This Row],[_min]]+10</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N139" s="1">
         <f>AVERAGE(Table1[[#This Row],[_min]:[_max]])</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O139" s="1" t="str">
         <f>Table1[[#This Row],[_units]]</f>
@@ -13678,15 +13675,15 @@
       </c>
       <c r="P139" s="1">
         <f>Table1[[#This Row],[_min]]</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q139" s="1">
         <f>Table1[[#This Row],[_max]]</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R139" s="1">
         <f>Table1[[#This Row],[_mean]]</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S139" s="1" t="str">
         <f t="shared" si="113"/>
@@ -13698,7 +13695,7 @@
       </c>
       <c r="U139" s="1" t="str">
         <f>_xlfn.CONCAT("{'low': ", Table1[[#This Row],[_std_min]], ", 'high': ",Table1[[#This Row],[_std_max]],"}")</f>
-        <v>{'low': 1, 'high': 11}</v>
+        <v>{'low': 5, 'high': 15}</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.5">
